--- a/output/Plantilla_Ajuste_Posproduccion.xlsx
+++ b/output/Plantilla_Ajuste_Posproduccion.xlsx
@@ -11655,7 +11655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C243"/>
+  <dimension ref="A1:C193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[CLAMICA04TM] CLÁSICA CAB AMARILLO NEÓN</t>
+          <t>[CLAMICA04TXL] CLÁSICA CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -11783,7 +11783,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[CLAMICA04TXL] CLÁSICA CAB AMARILLO NEÓN</t>
+          <t>[CLAMICA12TL] CLÁSICA CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -11798,11 +11798,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[CLAMICA12TL] CLÁSICA CAB AZUL MARINO</t>
+          <t>[CLAMICA16TXL] CLÁSICA CAB BLANCO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -11813,11 +11813,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[CLAMICA16TXL] CLÁSICA CAB BLANCO</t>
+          <t>[CLAMICA70TS] CLÁSICA CAB VINOTINTO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[CLAMICA70TS] CLÁSICA CAB VINOTINTO</t>
+          <t>[CLAMIDA16TM] CLÁSICA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -11843,7 +11843,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[CLAMIDA16TM] CLÁSICA DAMA BLANCO</t>
+          <t>[CLAMIDA16TXS] CLÁSICA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -11858,7 +11858,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[CLAMIDA16TXS] CLÁSICA DAMA BLANCO</t>
+          <t>[CLASPCA16TS] CLÁSICA SPORT LISO CAB BLANCO</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -11873,11 +11873,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[CLASPCA16TS] CLÁSICA SPORT LISO CAB BLANCO</t>
+          <t>[CLMSUCA152TM] MOTION CLÁSICA CAB VERDE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -11888,11 +11888,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[CLMSUCA152TM] MOTION CLÁSICA CAB VERDE</t>
+          <t>[DAYCSTCA43TS] DAILY CLÁSICA 3.0 CAB NEGRO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -11903,11 +11903,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[DAYCSTCA43TS] DAILY CLÁSICA 3.0 CAB NEGRO</t>
+          <t>[DOMBFCA16TM] DOMINIC CAB BLANCO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -11918,11 +11918,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[DAYCSTCA43TS] DAILY CLÁSICA 3.0 CAB NEGRO</t>
+          <t>[DOMBFCA16TS] DOMINIC CAB BLANCO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -11933,11 +11933,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[DOMBFCA16TM] DOMINIC CAB BLANCO</t>
+          <t>[GEMBADA16TL] VESTIDO GEMMA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[DOMBFCA16TM] DOMINIC CAB BLANCO</t>
+          <t>[GEMBADA16TM] VESTIDO GEMMA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -11963,11 +11963,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[DOMBFCA16TS] DOMINIC CAB BLANCO</t>
+          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -11978,11 +11978,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[GEMBADA16TL] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[GEOMACADA03TL] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -11993,11 +11993,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[GEMBADA16TL] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[GEOMACADA03TM] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[GEMBADA16TM] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[GEOMACADA03TS] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -12023,7 +12023,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[GEOMACADA03TXL] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -12038,11 +12038,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[HELBFDA30TM] HELEN DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -12053,11 +12053,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[HELBFDA30TXS] HELEN DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[GEOMACADA03TL] GEO MAYA DAMA Amarillo</t>
+          <t>[LARIMJDA16TXS] LARISA Dama Blanco</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -12083,11 +12083,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[GEOMACADA03TM] GEO MAYA DAMA Amarillo</t>
+          <t>[LMOFIDA31TS] LEGGING MOVA DAMA GRIS OSCURO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[GEOMACADA03TS] GEO MAYA DAMA Amarillo</t>
+          <t>[LMOFIDA31TXS] LEGGING MOVA DAMA GRIS OSCURO</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -12113,11 +12113,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[GEOMACADA03TXL] GEO MAYA DAMA Amarillo</t>
+          <t>[LMOFIDA43TM] LEGGING MOVA DAMA NEGRO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[HELBFDA30TM] HELEN DAMA GRIS CLARO</t>
+          <t>[MAADFDA30TM] ADVANCE MAFE DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -12143,7 +12143,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[HELBFDA30TXS] HELEN DAMA GRIS CLARO</t>
+          <t>[MAFMIDA16TS] MAFE DAMA BLANCO</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -12158,11 +12158,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[LARIMJDA16TXS] LARISA Dama Blanco</t>
+          <t>[MARMICA04TL] MAR CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -12173,11 +12173,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[LMOFIDA31TS] LEGGING MOVA DAMA GRIS OSCURO</t>
+          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -12188,11 +12188,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[LMOFIDA31TXS] LEGGING MOVA DAMA GRIS OSCURO</t>
+          <t>[MARMICA16T2XL] MAR CAB BLANCO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -12203,11 +12203,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[LMOFIDA43TM] LEGGING MOVA DAMA NEGRO</t>
+          <t>[MARMICA16TL] MAR CAB BLANCO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[MAADFDA30TM] ADVANCE MAFE DAMA GRIS CLARO</t>
+          <t>[MARMICA43TL] MAR CAB NEGRO</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -12233,11 +12233,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[MAFMIDA16TS] MAFE DAMA BLANCO</t>
+          <t>[MARMICA43TM] MAR CAB NEGRO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -12248,11 +12248,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[MARMICA04TL] MAR CAB AMARILLO NEÓN</t>
+          <t>[MARMICA43TS] MAR CAB NEGRO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
+          <t>[MARMICA50TM] MAR CAB ROJO</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -12278,11 +12278,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
+          <t>[MARMICA50TS] MAR CAB ROJO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -12293,11 +12293,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
+          <t>[MARMICA66T2XL] MAR CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -12308,11 +12308,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[MARMICA16T2XL] MAR CAB BLANCO</t>
+          <t>[MARMICA66TS] MAR CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[MARMICA16T2XL] MAR CAB BLANCO</t>
+          <t>[MARMIDA04TL] MAR DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -12338,7 +12338,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[MARMICA16TL] MAR CAB BLANCO</t>
+          <t>[MARMIDA12TS] MAR DAMA AZUL MARINO</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -12353,11 +12353,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[MARMICA43TL] MAR CAB NEGRO</t>
+          <t>[MARMIDA16TL] MAR DAMA BLANCO</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -12368,11 +12368,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[MARMICA43TM] MAR CAB NEGRO</t>
+          <t>[MARMIDA16TM] MAR DAMA BLANCO</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[MARMICA43TS] MAR CAB NEGRO</t>
+          <t>[MARMIDA16TS] MAR DAMA BLANCO</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -12398,7 +12398,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[MARMICA50TM] MAR CAB ROJO</t>
+          <t>[MARMIDA34TS] MAR DAMA LILA</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -12413,11 +12413,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[MARMICA50TS] MAR CAB ROJO</t>
+          <t>[MARMIDA34TXL] MAR DAMA LILA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -12428,11 +12428,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[MARMICA66T2XL] MAR CAB VERDE MILITAR</t>
+          <t>[MARMIDA48TXS] MAR DAMA PÚRPURA</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -12443,11 +12443,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[MARMICA66TS] MAR CAB VERDE MILITAR</t>
+          <t>[MARMIKI13T14] MAR KIDS AZUL REY</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[MARMIDA04TL] MAR DAMA AMARILLO NEÓN</t>
+          <t>[MARMIKI43T14] MAR KIDS NEGRO</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -12473,7 +12473,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[MARMIDA12TS] MAR DAMA AZUL MARINO</t>
+          <t>[MARMIKI50T10] MAR KIDS ROJO</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -12488,7 +12488,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[MARMIDA16TL] MAR DAMA BLANCO</t>
+          <t>[MARMIKI52T14] MAR KIDS ROSADO NEÓN</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -12503,11 +12503,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[MARMIDA16TL] MAR DAMA BLANCO</t>
+          <t>[MAYFNDA16TM] MAYA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[MARMIDA16TM] MAR DAMA BLANCO</t>
+          <t>[MAYFNDA16TXS] MAYA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -12533,7 +12533,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[MARMIDA16TS] MAR DAMA BLANCO</t>
+          <t>[MAYFNDA24TM] MAYA SPORT LITE DAMA CORAL NEÓN</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -12548,7 +12548,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[MARMIDA34TS] MAR DAMA LILA</t>
+          <t>[MIAMIDA11TM] MIA DAMA AZUL LAVANDA</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -12563,7 +12563,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[MARMIDA34TXL] MAR DAMA LILA</t>
+          <t>[MIKFNDA16TS] MIKA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -12578,7 +12578,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[MARMIDA48TXS] MAR DAMA PÚRPURA</t>
+          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -12593,7 +12593,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[MARMIKI13T14] MAR KIDS AZUL REY</t>
+          <t>[NAHFNCA16TL] NOAH SPORT LITE CAB BLANCO</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -12608,7 +12608,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[MARMIKI43T14] MAR KIDS NEGRO</t>
+          <t>[NAHFNCA24TL] NOAH SPORT LITE CAB CORAL NEÓN</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -12623,7 +12623,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[MARMIKI50T10] MAR KIDS ROJO</t>
+          <t>[NAHFNCA24TXL] NOAH SPORT LITE CAB CORAL NEÓN</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -12638,7 +12638,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[MARMIKI52T14] MAR KIDS ROSADO NEÓN</t>
+          <t>[PANNTCA12TL] EXPLORE PANTS CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -12653,7 +12653,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[MAYFNDA16TM] MAYA SPORT LITE DAMA BLANCO</t>
+          <t>[PANNTCA12TM] EXPLORE PANTS CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -12668,7 +12668,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[MAYFNDA16TM] MAYA SPORT LITE DAMA BLANCO</t>
+          <t>[PANNTCA12TS] EXPLORE PANTS CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -12683,7 +12683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[MAYFNDA16TXS] MAYA SPORT LITE DAMA BLANCO</t>
+          <t>[PANNTCA30TL] EXPLORE PANTS CAB GRIS CLARO</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -12698,7 +12698,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[MAYFNDA24TM] MAYA SPORT LITE DAMA CORAL NEÓN</t>
+          <t>[PANNTCA31TXL] EXPLORE PANTS CAB Gris Oscuro</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -12713,11 +12713,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[MIAMIDA11TM] MIA DAMA AZUL LAVANDA</t>
+          <t>[PANNTCA33TM] EXPLORE PANTS CAB KAKI</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[MIKFNDA16TS] MIKA SPORT LITE DAMA BLANCO</t>
+          <t>[PANNTCA33TXL] EXPLORE PANTS CAB KAKI</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -12743,7 +12743,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA BLANCO</t>
+          <t>[PANNTCA43TL] EXPLORE PANTS CAB NEGRO</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -12758,11 +12758,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[NAHFNCA16TL] NOAH SPORT LITE CAB BLANCO</t>
+          <t>[PANNTCA66TM] EXPLORE PANTS CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -12773,11 +12773,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TL] NOAH SPORT LITE CAB CORAL NEÓN</t>
+          <t>[PANNTCA66TS] EXPLORE PANTS CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TXL] NOAH SPORT LITE CAB CORAL NEÓN</t>
+          <t>[PANNTDA30TM] EXPLORE PANTS DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -12803,11 +12803,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[PANNTCA12TL] EXPLORE PANTS CAB AZUL MARINO</t>
+          <t>[PANNTDA33TM] EXPLORE PANTS DAMA KAKI</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -12818,11 +12818,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[PANNTCA12TM] EXPLORE PANTS CAB AZUL MARINO</t>
+          <t>[PANNTDA33TXL] EXPLORE PANTS DAMA KAKI</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[PANNTCA12TS] EXPLORE PANTS CAB AZUL MARINO</t>
+          <t>[PANNTDA43TM] EXPLORE PANTS DAMA NEGRO</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -12848,7 +12848,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[PANNTCA30TL] EXPLORE PANTS CAB GRIS CLARO</t>
+          <t>[PANNTDA43TXL] EXPLORE PANTS DAMA NEGRO</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -12863,7 +12863,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[PANNTCA31TXL] EXPLORE PANTS CAB Gris Oscuro</t>
+          <t>[PANNTDA43TXS] EXPLORE PANTS DAMA NEGRO</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -12878,11 +12878,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[PANNTCA33TM] EXPLORE PANTS CAB KAKI</t>
+          <t>[PANNTDA66TM] EXPLORE PANTS DAMA VERDE MILITAR</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[PANNTCA33TXL] EXPLORE PANTS CAB KAKI</t>
+          <t>[PANNTDA66TXL] EXPLORE PANTS DAMA VERDE MILITAR</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -12908,11 +12908,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[PANNTCA43TL] EXPLORE PANTS CAB NEGRO</t>
+          <t>[RIOMICA04TM] RIO CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12923,11 +12923,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[PANNTCA66TM] EXPLORE PANTS CAB VERDE MILITAR</t>
+          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12938,11 +12938,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[PANNTCA66TS] EXPLORE PANTS CAB VERDE MILITAR</t>
+          <t>[RIOMICA11T2XL] RIO CAB AZUL LAVANDA</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12953,11 +12953,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[PANNTDA30TM] EXPLORE PANTS DAMA GRIS CLARO</t>
+          <t>[RIOMICA16T2XL] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12968,11 +12968,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[PANNTDA33TM] EXPLORE PANTS DAMA KAKI</t>
+          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12983,11 +12983,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[PANNTDA33TXL] EXPLORE PANTS DAMA KAKI</t>
+          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12998,11 +12998,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[PANNTDA43TM] EXPLORE PANTS DAMA NEGRO</t>
+          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13013,11 +13013,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[PANNTDA43TXL] EXPLORE PANTS DAMA NEGRO</t>
+          <t>[RIOMICA16TXL] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13028,11 +13028,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[PANNTDA43TXS] EXPLORE PANTS DAMA NEGRO</t>
+          <t>[RIOMICA30TM] RIO CAB GRIS CLARO</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[PANNTDA66TM] EXPLORE PANTS DAMA VERDE MILITAR</t>
+          <t>[RIOMICA52TM] RIO CAB ROSADO NEÓN</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -13058,11 +13058,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[PANNTDA66TXL] EXPLORE PANTS DAMA VERDE MILITAR</t>
+          <t>[RIOMICA66T2XL] RIO CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13073,11 +13073,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[RIOMICA04TM] RIO CAB AMARILLO NEÓN</t>
+          <t>[RIOMICA70TXL] RIO CAB VINOTINTO</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
+          <t>[RIOMIDA01TM] RIO DAMA AGUAMARINA</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -13103,11 +13103,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
+          <t>[RIOMIDA04TL] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13118,11 +13118,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
+          <t>[RIOMIDA04TM] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13133,11 +13133,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[RIOMICA11T2XL] RIO CAB AZUL LAVANDA</t>
+          <t>[RIOMIDA04TS] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13148,11 +13148,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[RIOMICA16T2XL] RIO CAB BLANCO</t>
+          <t>[RIOMIDA04TXL] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13163,11 +13163,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[RIOMICA16T2XL] RIO CAB BLANCO</t>
+          <t>[RIOMIDA04TXS] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13178,11 +13178,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
+          <t>[RIOMIDA11TXS] RIO DAMA AZUL LAVANDA</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13193,11 +13193,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
+          <t>[RIOMIDA16TL] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13208,11 +13208,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
+          <t>[RIOMIDA16TM] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13223,11 +13223,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
+          <t>[RIOMIDA16TS] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13238,11 +13238,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
+          <t>[RIOMIDA16TXS] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13253,11 +13253,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
+          <t>[RIOMIDA34TS] RIO DAMA LILA</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
+          <t>[RIOMIDA48TXS] RIO DAMA PÚRPURA</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -13283,11 +13283,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
+          <t>[RIOMIDA52TXL] RIO DAMA ROSADO NEÓN</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13298,11 +13298,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
+          <t>[RIOMIDA66TXL] RIO DAMA VERDE MILITAR</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13313,11 +13313,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
+          <t>[RIOMIKI66T2] RIO KIDS VERDE MILITAR</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13328,11 +13328,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>[RIOMICA16TXL] RIO CAB BLANCO</t>
+          <t>[SARSPDA16TS] FALDA SARA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13343,11 +13343,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>[RIOMICA30TM] RIO CAB GRIS CLARO</t>
+          <t>[SARSPDA16TXL] FALDA SARA DAMA BLANCO</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13358,11 +13358,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>[RIOMICA30TM] RIO CAB GRIS CLARO</t>
+          <t>[SARSPKI16T10] FALDA SARA KIDS BLANCO</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13373,11 +13373,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>[RIOMICA52TM] RIO CAB ROSADO NEÓN</t>
+          <t>[SARSPKI16T8] FALDA SARA KIDS BLANCO</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13388,11 +13388,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>[RIOMICA66T2XL] RIO CAB VERDE MILITAR</t>
+          <t>[SHONRCA12TS] SHORT SPORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13403,11 +13403,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>[RIOMICA70TXL] RIO CAB VINOTINTO</t>
+          <t>[SHONTCA12TL] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13418,11 +13418,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>[RIOMIDA01TM] RIO DAMA AGUAMARINA</t>
+          <t>[SHONTCA12TM] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13433,11 +13433,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>[RIOMIDA01TM] RIO DAMA AGUAMARINA</t>
+          <t>[SHONTCA12TS] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13448,11 +13448,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA12TXL] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13463,11 +13463,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA30TS] EXPLORE SHORT CAB GRIS CLARO</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TM] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA31TL] EXPLORE SHORT CAB Gris Oscuro</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -13493,11 +13493,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TM] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA31TXL] EXPLORE SHORT CAB Gris Oscuro</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13508,11 +13508,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TS] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA33TL] EXPLORE SHORT  CAB KAKI</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13523,11 +13523,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA43TS] EXPLORE SHORT CAB NEGRO</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA66TL] EXPLORE SHORT CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -13553,7 +13553,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXS] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -13568,11 +13568,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXS] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13583,11 +13583,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TXS] RIO DAMA AZUL LAVANDA</t>
+          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TL] RIO DAMA BLANCO</t>
+          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -13613,11 +13613,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TM] RIO DAMA BLANCO</t>
+          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13628,11 +13628,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TS] RIO DAMA BLANCO</t>
+          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13643,11 +13643,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TS] RIO DAMA BLANCO</t>
+          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -13658,11 +13658,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXS] RIO DAMA BLANCO</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -13673,11 +13673,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXS] RIO DAMA BLANCO</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -13688,11 +13688,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>[RIOMIDA34TS] RIO DAMA LILA</t>
+          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -13703,11 +13703,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TXS] RIO DAMA PÚRPURA</t>
+          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -13718,11 +13718,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>[RIOMIDA52TXL] RIO DAMA ROSADO NEÓN</t>
+          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -13733,11 +13733,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXL] RIO DAMA VERDE MILITAR</t>
+          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -13748,11 +13748,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>[RIOMIKI66T2] RIO KIDS VERDE MILITAR</t>
+          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -13763,11 +13763,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>[SARSPDA16TS] FALDA SARA DAMA BLANCO</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -13778,11 +13778,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>[SARSPDA16TXL] FALDA SARA DAMA BLANCO</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -13793,11 +13793,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>[SARSPKI16T10] FALDA SARA KIDS BLANCO</t>
+          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -13808,11 +13808,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>[SARSPKI16T10] FALDA SARA KIDS BLANCO</t>
+          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -13823,11 +13823,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>[SARSPKI16T8] FALDA SARA KIDS BLANCO</t>
+          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -13838,11 +13838,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>[SHONRCA12TS] SHORT SPORT CAB AZUL MARINO</t>
+          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -13853,11 +13853,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>[SHONTCA12TL] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -13868,11 +13868,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>[SHONTCA12TM] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -13883,11 +13883,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>[SHONTCA12TS] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>[SHONTCA12TXL] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -13913,11 +13913,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>[SHONTCA30TS] EXPLORE SHORT CAB GRIS CLARO</t>
+          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -13928,11 +13928,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>[SHONTCA31TL] EXPLORE SHORT CAB Gris Oscuro</t>
+          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -13943,11 +13943,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>[SHONTCA31TXL] EXPLORE SHORT CAB Gris Oscuro</t>
+          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -13958,11 +13958,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>[SHONTCA33TL] EXPLORE SHORT  CAB KAKI</t>
+          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -13973,11 +13973,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>[SHONTCA43TS] EXPLORE SHORT CAB NEGRO</t>
+          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -13988,11 +13988,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>[SHONTCA66TL] EXPLORE SHORT CAB VERDE MILITAR</t>
+          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -14003,11 +14003,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -14018,11 +14018,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -14033,11 +14033,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -14048,11 +14048,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -14063,11 +14063,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -14078,11 +14078,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -14093,11 +14093,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -14108,11 +14108,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -14123,11 +14123,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -14138,11 +14138,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -14153,11 +14153,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -14168,11 +14168,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -14183,11 +14183,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -14198,11 +14198,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -14213,11 +14213,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -14228,11 +14228,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -14243,11 +14243,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -14258,11 +14258,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
+          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -14273,11 +14273,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
+          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -14288,11 +14288,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -14303,11 +14303,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -14318,11 +14318,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB NEGRO</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -14333,11 +14333,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB NEGRO</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -14348,11 +14348,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB NEGRO</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -14363,11 +14363,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHUNTDA43TM] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -14378,11 +14378,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHUNTDA43TS] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -14393,11 +14393,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHUNTDA43TXL] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -14408,11 +14408,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHUNTDA43TXS] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -14423,11 +14423,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTACA12TL] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTACA12TM] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -14453,11 +14453,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTACA12TXL] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -14468,11 +14468,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTACA12TXS] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -14483,11 +14483,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTADA12TL] TOP ALGODON DAMA Azul marino</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -14498,11 +14498,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTADA12TM] TOP ALGODON DAMA Azul marino</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -14513,11 +14513,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[TALGTADA12TS] TOP ALGODON DAMA Azul marino</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -14528,11 +14528,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[VIVMIDA43TM] VIVI DAMA NEGRO</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -14543,763 +14543,13 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[VIVMIDA48TXL] VIVI DAMA PÚRPURA</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C193" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>6</v>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>3</v>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>2</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>5</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>6</v>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>2</v>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>3</v>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>1</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>4</v>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>3</v>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>3</v>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>2</v>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>1</v>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>2</v>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>1</v>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>1</v>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>1</v>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>1</v>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>2</v>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>3</v>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>1</v>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>1</v>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>2</v>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>1</v>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>2</v>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>3</v>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>1</v>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>5</v>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>3</v>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>4</v>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>4</v>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>4</v>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>2</v>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>1</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>1</v>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>1</v>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>1</v>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>[SHUNTDA43TM] SHORT SPORT R1 DAMA NEGRO</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>6</v>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>[SHUNTDA43TS] SHORT SPORT R1 DAMA NEGRO</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>17</v>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>[SHUNTDA43TXL] SHORT SPORT R1 DAMA NEGRO</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>2</v>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>[SHUNTDA43TXS] SHORT SPORT R1 DAMA NEGRO</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>20</v>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>[TALGTACA12TL] TOP ALGODON CAB Azul marino</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>1</v>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>[TALGTACA12TM] TOP ALGODON CAB Azul marino</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>1</v>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>[TALGTACA12TXL] TOP ALGODON CAB Azul marino</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>1</v>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>[TALGTACA12TXS] TOP ALGODON CAB Azul marino</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>1</v>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>[TALGTADA12TL] TOP ALGODON DAMA Azul marino</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>1</v>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>[TALGTADA12TM] TOP ALGODON DAMA Azul marino</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>1</v>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>[TALGTADA12TS] TOP ALGODON DAMA Azul marino</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>1</v>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>[VIVMIDA43TM] VIVI DAMA NEGRO</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>3</v>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>[VIVMIDA48TXL] VIVI DAMA PÚRPURA</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>1</v>
-      </c>
-      <c r="C243" t="inlineStr">
         <is>
           <t>TH/Posproducción</t>
         </is>
@@ -15316,7 +14566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F560"/>
+  <dimension ref="A1:F510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24869,16 +24119,16 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>RIOMIDA16TXS</t>
+          <t>BACCCDA158TL</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXS] RIO DAMA BLANCO</t>
+          <t>[BACCCDA158TL] BASIC LINE CROP TEE DAMA CREMA</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -24899,12 +24149,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MARMICA16T2XL</t>
+          <t>BACCCDA158TM</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>[MARMICA16T2XL] MAR CAB BLANCO</t>
+          <t>[BACCCDA158TM] BASIC LINE CROP TEE DAMA CREMA</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -24929,16 +24179,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>LARIMJDA16TXS</t>
+          <t>BACCCDA43TS</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>[LARIMJDA16TXS] LARISA Dama Blanco</t>
+          <t>[BACCCDA43TS] BASIC LINE CROP TEE DAMA NEGRO</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -24959,12 +24209,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DOMBFCA16TM</t>
+          <t>BAOCCCA158TM</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>[DOMBFCA16TM] DOMINIC CAB BLANCO</t>
+          <t>[BAOCCCA158TM] BASIC LINE OVERSIZED CAB CREMA</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -24989,16 +24239,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>RIOMIDA04TXL</t>
+          <t>BAOCCCA158TS</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[BAOCCCA158TS] BASIC LINE OVERSIZED CAB CREMA</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -25028,7 +24278,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -25049,12 +24299,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MARMICA04TXL</t>
+          <t>CLAMICA04TXL</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
+          <t>[CLAMICA04TXL] CLÁSICA CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -25079,16 +24329,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DOMBFCA16TS</t>
+          <t>CLAMICA12TL</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>[DOMBFCA16TS] DOMINIC CAB BLANCO</t>
+          <t>[CLAMICA12TL] CLÁSICA CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -25109,16 +24359,16 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>MARMIDA16TL</t>
+          <t>CLAMICA16TXL</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>[MARMIDA16TL] MAR DAMA BLANCO</t>
+          <t>[CLAMICA16TXL] CLÁSICA CAB BLANCO</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -25139,12 +24389,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>MIKFNDA16TS</t>
+          <t>CLAMICA70TS</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>[MIKFNDA16TS] MIKA SPORT LITE DAMA BLANCO</t>
+          <t>[CLAMICA70TS] CLÁSICA CAB VINOTINTO</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -25169,12 +24419,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>RIOMICA16T2XL</t>
+          <t>CLAMIDA16TM</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>[RIOMICA16T2XL] RIO CAB BLANCO</t>
+          <t>[CLAMIDA16TM] CLÁSICA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D329" t="n">
@@ -25199,12 +24449,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>MAFMIDA16TS</t>
+          <t>CLAMIDA16TXS</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>[MAFMIDA16TS] MAFE DAMA BLANCO</t>
+          <t>[CLAMIDA16TXS] CLÁSICA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -25229,16 +24479,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>GEMBADA16TL</t>
+          <t>CLASPCA16TS</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>[GEMBADA16TL] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[CLASPCA16TS] CLÁSICA SPORT LISO CAB BLANCO</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -25259,16 +24509,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>RIOMICA16T2XL</t>
+          <t>CLMSUCA152TM</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>[RIOMICA16T2XL] RIO CAB BLANCO</t>
+          <t>[CLMSUCA152TM] MOTION CLÁSICA CAB VERDE</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -25289,16 +24539,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MARMICA16TL</t>
+          <t>DAYCSTCA43TS</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>[MARMICA16TL] MAR CAB BLANCO</t>
+          <t>[DAYCSTCA43TS] DAILY CLÁSICA 3.0 CAB NEGRO</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -25319,16 +24569,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RIOMICA16TS</t>
+          <t>DOMBFCA16TM</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
+          <t>[DOMBFCA16TM] DOMINIC CAB BLANCO</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -25349,16 +24599,16 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>GEMBADA16TXS</t>
+          <t>DOMBFCA16TS</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[DOMBFCA16TS] DOMINIC CAB BLANCO</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -25379,16 +24629,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RIOMICA16TL</t>
+          <t>GEMBADA16TL</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
+          <t>[GEMBADA16TL] VESTIDO GEMMA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -25409,16 +24659,16 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>SARSPKI16T8</t>
+          <t>GEMBADA16TM</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>[SARSPKI16T8] FALDA SARA KIDS BLANCO</t>
+          <t>[GEMBADA16TM] VESTIDO GEMMA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -25439,16 +24689,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>CLAMICA16TXL</t>
+          <t>GEMBADA16TXS</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>[CLAMICA16TXL] CLÁSICA CAB BLANCO</t>
+          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -25469,12 +24719,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MARMIDA16TS</t>
+          <t>GEOMACADA03TL</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>[MARMIDA16TS] MAR DAMA BLANCO</t>
+          <t>[GEOMACADA03TL] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -25499,16 +24749,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MARMICA50TM</t>
+          <t>GEOMACADA03TM</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>[MARMICA50TM] MAR CAB ROJO</t>
+          <t>[GEOMACADA03TM] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -25529,16 +24779,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RIOMICA66T2XL</t>
+          <t>GEOMACADA03TS</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>[RIOMICA66T2XL] RIO CAB VERDE MILITAR</t>
+          <t>[GEOMACADA03TS] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -25559,16 +24809,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RIOMICA30TM</t>
+          <t>GEOMACADA03TXL</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>[RIOMICA30TM] RIO CAB GRIS CLARO</t>
+          <t>[GEOMACADA03TXL] GEO MAYA DAMA Amarillo</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -25589,16 +24839,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>SHONTCA12TXL</t>
+          <t>HELBFDA30TM</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>[SHONTCA12TXL] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[HELBFDA30TM] HELEN DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -25619,16 +24869,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SHONTCA12TL</t>
+          <t>HELBFDA30TXS</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>[SHONTCA12TL] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[HELBFDA30TXS] HELEN DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -25649,16 +24899,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>SHONTCA12TM</t>
+          <t>LARIMJDA16TXS</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>[SHONTCA12TM] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[LARIMJDA16TXS] LARISA Dama Blanco</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -25679,16 +24929,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>SHONTCA12TS</t>
+          <t>LMOFIDA31TS</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>[SHONTCA12TS] EXPLORE SHORT CAB AZUL MARINO</t>
+          <t>[LMOFIDA31TS] LEGGING MOVA DAMA GRIS OSCURO</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -25709,12 +24959,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MARMIDA12TS</t>
+          <t>LMOFIDA31TXS</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>[MARMIDA12TS] MAR DAMA AZUL MARINO</t>
+          <t>[LMOFIDA31TXS] LEGGING MOVA DAMA GRIS OSCURO</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -25739,12 +24989,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>SHOSUKI155T14</t>
+          <t>LMOFIDA43TM</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[LMOFIDA43TM] LEGGING MOVA DAMA NEGRO</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -25769,12 +25019,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SHOSUKI155T2</t>
+          <t>MAADFDA30TM</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MAADFDA30TM] ADVANCE MAFE DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -25799,16 +25049,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>SHOSUKI153T12</t>
+          <t>MAFMIDA16TS</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[MAFMIDA16TS] MAFE DAMA BLANCO</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -25829,16 +25079,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>SHOSUKI153T1</t>
+          <t>MARMICA04TL</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[MARMICA04TL] MAR CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -25859,16 +25109,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>SHOSUKI153T12</t>
+          <t>MARMICA04TXL</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -25889,16 +25139,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>SHOSUKI153T12</t>
+          <t>MARMICA16T2XL</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[MARMICA16T2XL] MAR CAB BLANCO</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -25919,12 +25169,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>SHOSUKI153T8</t>
+          <t>MARMICA16TL</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[MARMICA16TL] MAR CAB BLANCO</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -25949,16 +25199,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>SHOSUKI154T6</t>
+          <t>MARMICA43TL</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[MARMICA43TL] MAR CAB NEGRO</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -25979,16 +25229,16 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SHOSUKI154T4</t>
+          <t>MARMICA43TM</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[MARMICA43TM] MAR CAB NEGRO</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -26009,16 +25259,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SHOSUKI156T2</t>
+          <t>MARMICA43TS</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[MARMICA43TS] MAR CAB NEGRO</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -26039,12 +25289,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>SHOSUKI155T6</t>
+          <t>MARMICA50TM</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MARMICA50TM] MAR CAB ROJO</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -26069,16 +25319,16 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SHOSUKI155T8</t>
+          <t>MARMICA50TS</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MARMICA50TS] MAR CAB ROJO</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -26099,16 +25349,16 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>SHOSUKI155T2</t>
+          <t>MARMICA66T2XL</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MARMICA66T2XL] MAR CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -26129,16 +25379,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>SHOSUKI155T4</t>
+          <t>MARMICA66TS</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MARMICA66TS] MAR CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -26159,12 +25409,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>SHOSUKI155T6</t>
+          <t>MARMIDA04TL</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MARMIDA04TL] MAR DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -26189,12 +25439,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>SHOSUKI155T12</t>
+          <t>MARMIDA12TS</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[MARMIDA12TS] MAR DAMA AZUL MARINO</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -26219,16 +25469,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MARMIKI50T10</t>
+          <t>MARMIDA16TL</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>[MARMIKI50T10] MAR KIDS ROJO</t>
+          <t>[MARMIDA16TL] MAR DAMA BLANCO</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -26249,16 +25499,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>CLMSUCA152TM</t>
+          <t>MARMIDA16TM</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>[CLMSUCA152TM] MOTION CLÁSICA CAB VERDE</t>
+          <t>[MARMIDA16TM] MAR DAMA BLANCO</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -26279,16 +25529,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PANNTDA33TM</t>
+          <t>MARMIDA16TS</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>[PANNTDA33TM] EXPLORE PANTS DAMA KAKI</t>
+          <t>[MARMIDA16TS] MAR DAMA BLANCO</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -26309,16 +25559,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PANNTCA33TM</t>
+          <t>MARMIDA34TS</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>[PANNTCA33TM] EXPLORE PANTS CAB KAKI</t>
+          <t>[MARMIDA34TS] MAR DAMA LILA</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -26339,12 +25589,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PANNTCA33TXL</t>
+          <t>MARMIDA34TXL</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>[PANNTCA33TXL] EXPLORE PANTS CAB KAKI</t>
+          <t>[MARMIDA34TXL] MAR DAMA LILA</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -26369,16 +25619,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PANNTDA33TXL</t>
+          <t>MARMIDA48TXS</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>[PANNTDA33TXL] EXPLORE PANTS DAMA KAKI</t>
+          <t>[MARMIDA48TXS] MAR DAMA PÚRPURA</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -26399,12 +25649,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PANNTCA30TL</t>
+          <t>MARMIKI13T14</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>[PANNTCA30TL] EXPLORE PANTS CAB GRIS CLARO</t>
+          <t>[MARMIKI13T14] MAR KIDS AZUL REY</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -26429,12 +25679,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PANNTDA30TM</t>
+          <t>MARMIKI43T14</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>[PANNTDA30TM] EXPLORE PANTS DAMA GRIS CLARO</t>
+          <t>[MARMIKI43T14] MAR KIDS NEGRO</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -26459,12 +25709,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PANNTCA31TXL</t>
+          <t>MARMIKI50T10</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>[PANNTCA31TXL] EXPLORE PANTS CAB Gris Oscuro</t>
+          <t>[MARMIKI50T10] MAR KIDS ROJO</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -26489,12 +25739,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PANNTCA12TL</t>
+          <t>MARMIKI52T14</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>[PANNTCA12TL] EXPLORE PANTS CAB AZUL MARINO</t>
+          <t>[MARMIKI52T14] MAR KIDS ROSADO NEÓN</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -26519,16 +25769,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PANNTCA12TS</t>
+          <t>MAYFNDA16TM</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>[PANNTCA12TS] EXPLORE PANTS CAB AZUL MARINO</t>
+          <t>[MAYFNDA16TM] MAYA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -26549,12 +25799,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PANNTCA12TM</t>
+          <t>MAYFNDA16TXS</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>[PANNTCA12TM] EXPLORE PANTS CAB AZUL MARINO</t>
+          <t>[MAYFNDA16TXS] MAYA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -26579,12 +25829,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PANNTDA43TXS</t>
+          <t>MAYFNDA24TM</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>[PANNTDA43TXS] EXPLORE PANTS DAMA NEGRO</t>
+          <t>[MAYFNDA24TM] MAYA SPORT LITE DAMA CORAL NEÓN</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -26609,12 +25859,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PANNTDA43TM</t>
+          <t>MIAMIDA11TM</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>[PANNTDA43TM] EXPLORE PANTS DAMA NEGRO</t>
+          <t>[MIAMIDA11TM] MIA DAMA AZUL LAVANDA</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -26639,12 +25889,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PANNTDA43TXL</t>
+          <t>MIKFNDA16TS</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>[PANNTDA43TXL] EXPLORE PANTS DAMA NEGRO</t>
+          <t>[MIKFNDA16TS] MIKA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -26669,12 +25919,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PANNTCA43TL</t>
+          <t>MIKFNDA16TXS</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>[PANNTCA43TL] EXPLORE PANTS CAB NEGRO</t>
+          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA BLANCO</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -26699,12 +25949,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PANNTDA66TXL</t>
+          <t>NAHFNCA16TL</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>[PANNTDA66TXL] EXPLORE PANTS DAMA VERDE MILITAR</t>
+          <t>[NAHFNCA16TL] NOAH SPORT LITE CAB BLANCO</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -26729,12 +25979,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PANNTDA66TM</t>
+          <t>NAHFNCA24TL</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>[PANNTDA66TM] EXPLORE PANTS DAMA VERDE MILITAR</t>
+          <t>[NAHFNCA24TL] NOAH SPORT LITE CAB CORAL NEÓN</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -26759,16 +26009,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PANNTCA66TM</t>
+          <t>NAHFNCA24TXL</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>[PANNTCA66TM] EXPLORE PANTS CAB VERDE MILITAR</t>
+          <t>[NAHFNCA24TXL] NOAH SPORT LITE CAB CORAL NEÓN</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -26789,16 +26039,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PANNTCA66TS</t>
+          <t>PANNTCA12TL</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>[PANNTCA66TS] EXPLORE PANTS CAB VERDE MILITAR</t>
+          <t>[PANNTCA12TL] EXPLORE PANTS CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -26819,16 +26069,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>RIOMICA30TM</t>
+          <t>PANNTCA12TM</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>[RIOMICA30TM] RIO CAB GRIS CLARO</t>
+          <t>[PANNTCA12TM] EXPLORE PANTS CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -26849,16 +26099,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SHOSUKI153T12</t>
+          <t>PANNTCA12TS</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA12TS] EXPLORE PANTS CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -26879,16 +26129,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>SHOSUKI153T10</t>
+          <t>PANNTCA30TL</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA30TL] EXPLORE PANTS CAB GRIS CLARO</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -26909,16 +26159,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>SHOSUKI153T14</t>
+          <t>PANNTCA31TXL</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA31TXL] EXPLORE PANTS CAB Gris Oscuro</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -26939,16 +26189,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SHOSUKI153T8</t>
+          <t>PANNTCA33TM</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA33TM] EXPLORE PANTS CAB KAKI</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -26969,16 +26219,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>SHOSUKI153T6</t>
+          <t>PANNTCA33TXL</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA33TXL] EXPLORE PANTS CAB KAKI</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -26999,16 +26249,16 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SHOSUKI153T1</t>
+          <t>PANNTCA43TL</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA43TL] EXPLORE PANTS CAB NEGRO</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -27029,16 +26279,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>SHOSUKI153T4</t>
+          <t>PANNTCA66TM</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[PANNTCA66TM] EXPLORE PANTS CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -27059,16 +26309,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SHOSUKI156T1</t>
+          <t>PANNTCA66TS</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTCA66TS] EXPLORE PANTS CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -27089,16 +26339,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>SHOSUKI156T10</t>
+          <t>PANNTDA30TM</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA30TM] EXPLORE PANTS DAMA GRIS CLARO</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -27119,16 +26369,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>SHOSUKI156T14</t>
+          <t>PANNTDA33TM</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA33TM] EXPLORE PANTS DAMA KAKI</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -27149,16 +26399,16 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>SHOSUKI156T4</t>
+          <t>PANNTDA33TXL</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA33TXL] EXPLORE PANTS DAMA KAKI</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -27179,16 +26429,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SHOSUKI156T12</t>
+          <t>PANNTDA43TM</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA43TM] EXPLORE PANTS DAMA NEGRO</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -27209,16 +26459,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SHOSUKI156T6</t>
+          <t>PANNTDA43TXL</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA43TXL] EXPLORE PANTS DAMA NEGRO</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -27239,16 +26489,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>SHOSUKI156T2</t>
+          <t>PANNTDA43TXS</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA43TXS] EXPLORE PANTS DAMA NEGRO</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -27269,16 +26519,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>SHOSUKI156T8</t>
+          <t>PANNTDA66TM</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
+          <t>[PANNTDA66TM] EXPLORE PANTS DAMA VERDE MILITAR</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -27299,16 +26549,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SHOSUKI154T10</t>
+          <t>PANNTDA66TXL</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[PANNTDA66TXL] EXPLORE PANTS DAMA VERDE MILITAR</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -27329,16 +26579,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SHOSUKI154T14</t>
+          <t>RIOMICA04TM</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[RIOMICA04TM] RIO CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -27359,16 +26609,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>SHOSUKI154T12</t>
+          <t>RIOMICA04TXL</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -27389,16 +26639,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>SHOSUKI154T8</t>
+          <t>RIOMICA11T2XL</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[RIOMICA11T2XL] RIO CAB AZUL LAVANDA</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -27419,12 +26669,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>SHOSUKI154T2</t>
+          <t>RIOMICA16T2XL</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[RIOMICA16T2XL] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -27449,16 +26699,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>SHOSUKI154T4</t>
+          <t>RIOMICA16TL</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -27479,16 +26729,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>SHOSUKI154T1</t>
+          <t>RIOMICA16TM</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -27509,16 +26759,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>RIOMIDA66TXL</t>
+          <t>RIOMICA16TS</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXL] RIO DAMA VERDE MILITAR</t>
+          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -27539,16 +26789,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>MARMICA50TS</t>
+          <t>RIOMICA16TXL</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>[MARMICA50TS] MAR CAB ROJO</t>
+          <t>[RIOMICA16TXL] RIO CAB BLANCO</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -27569,16 +26819,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>MARMICA66T2XL</t>
+          <t>RIOMICA30TM</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>[MARMICA66T2XL] MAR CAB VERDE MILITAR</t>
+          <t>[RIOMICA30TM] RIO CAB GRIS CLARO</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -27599,16 +26849,16 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>MARMICA66TS</t>
+          <t>RIOMICA52TM</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>[MARMICA66TS] MAR CAB VERDE MILITAR</t>
+          <t>[RIOMICA52TM] RIO CAB ROSADO NEÓN</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -27629,16 +26879,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>RIOMICA70TXL</t>
+          <t>RIOMICA66T2XL</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>[RIOMICA70TXL] RIO CAB VINOTINTO</t>
+          <t>[RIOMICA66T2XL] RIO CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -27659,12 +26909,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>MARMIKI13T14</t>
+          <t>RIOMICA70TXL</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>[MARMIKI13T14] MAR KIDS AZUL REY</t>
+          <t>[RIOMICA70TXL] RIO CAB VINOTINTO</t>
         </is>
       </c>
       <c r="D412" t="n">
@@ -27689,16 +26939,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>SHONRCA12TS</t>
+          <t>RIOMIDA01TM</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>[SHONRCA12TS] SHORT SPORT CAB AZUL MARINO</t>
+          <t>[RIOMIDA01TM] RIO DAMA AGUAMARINA</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -27719,16 +26969,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>CLASPCA16TS</t>
+          <t>RIOMIDA04TL</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>[CLASPCA16TS] CLÁSICA SPORT LISO CAB BLANCO</t>
+          <t>[RIOMIDA04TL] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -27749,16 +26999,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MARMIDA48TXS</t>
+          <t>RIOMIDA04TM</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>[MARMIDA48TXS] MAR DAMA PÚRPURA</t>
+          <t>[RIOMIDA04TM] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -27779,16 +27029,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>CLAMICA12TL</t>
+          <t>RIOMIDA04TS</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>[CLAMICA12TL] CLÁSICA CAB AZUL MARINO</t>
+          <t>[RIOMIDA04TS] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -27809,16 +27059,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>TALGTACA12TXL</t>
+          <t>RIOMIDA04TXL</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>[TALGTACA12TXL] TOP ALGODON CAB Azul marino</t>
+          <t>[RIOMIDA04TXL] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -27839,16 +27089,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>TALGTACA12TM</t>
+          <t>RIOMIDA04TXS</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>[TALGTACA12TM] TOP ALGODON CAB Azul marino</t>
+          <t>[RIOMIDA04TXS] RIO DAMA AMARILLO NEÓN</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -27869,12 +27119,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>TALGTACA12TL</t>
+          <t>RIOMIDA11TXS</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>[TALGTACA12TL] TOP ALGODON CAB Azul marino</t>
+          <t>[RIOMIDA11TXS] RIO DAMA AZUL LAVANDA</t>
         </is>
       </c>
       <c r="D419" t="n">
@@ -27899,16 +27149,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>TALGTACA12TXS</t>
+          <t>RIOMIDA16TL</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>[TALGTACA12TXS] TOP ALGODON CAB Azul marino</t>
+          <t>[RIOMIDA16TL] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -27929,12 +27179,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>TALGTADA12TS</t>
+          <t>RIOMIDA16TM</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>[TALGTADA12TS] TOP ALGODON DAMA Azul marino</t>
+          <t>[RIOMIDA16TM] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -27959,16 +27209,16 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>TALGTADA12TL</t>
+          <t>RIOMIDA16TS</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>[TALGTADA12TL] TOP ALGODON DAMA Azul marino</t>
+          <t>[RIOMIDA16TS] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -27989,16 +27239,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>TALGTADA12TM</t>
+          <t>RIOMIDA16TXS</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>[TALGTADA12TM] TOP ALGODON DAMA Azul marino</t>
+          <t>[RIOMIDA16TXS] RIO DAMA BLANCO</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -28019,16 +27269,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>RIOMIKI66T2</t>
+          <t>RIOMIDA34TS</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>[RIOMIKI66T2] RIO KIDS VERDE MILITAR</t>
+          <t>[RIOMIDA34TS] RIO DAMA LILA</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -28049,16 +27299,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SHUNTDA43TXS</t>
+          <t>RIOMIDA48TXS</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>[SHUNTDA43TXS] SHORT SPORT R1 DAMA NEGRO</t>
+          <t>[RIOMIDA48TXS] RIO DAMA PÚRPURA</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -28079,16 +27329,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SHUNTDA43TS</t>
+          <t>RIOMIDA52TXL</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>[SHUNTDA43TS] SHORT SPORT R1 DAMA NEGRO</t>
+          <t>[RIOMIDA52TXL] RIO DAMA ROSADO NEÓN</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -28109,16 +27359,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SHOSPBFDA207TS</t>
+          <t>RIOMIDA66TXL</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[RIOMIDA66TXL] RIO DAMA VERDE MILITAR</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -28139,16 +27389,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SHUNTDA43TM</t>
+          <t>RIOMIKI66T2</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>[SHUNTDA43TM] SHORT SPORT R1 DAMA NEGRO</t>
+          <t>[RIOMIKI66T2] RIO KIDS VERDE MILITAR</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -28169,16 +27419,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>SHUNTDA43TXL</t>
+          <t>SARSPDA16TS</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>[SHUNTDA43TXL] SHORT SPORT R1 DAMA NEGRO</t>
+          <t>[SARSPDA16TS] FALDA SARA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -28199,16 +27449,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SHOSPBFCA207TS</t>
+          <t>SARSPDA16TXL</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SARSPDA16TXL] FALDA SARA DAMA BLANCO</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -28229,16 +27479,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SHOSPBFCA207TS</t>
+          <t>SARSPKI16T10</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SARSPKI16T10] FALDA SARA KIDS BLANCO</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -28259,16 +27509,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>SHUNTCA43TM</t>
+          <t>SARSPKI16T8</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB NEGRO</t>
+          <t>[SARSPKI16T8] FALDA SARA KIDS BLANCO</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -28289,12 +27539,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>SHUNTCA43T2XL</t>
+          <t>SHONRCA12TS</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB NEGRO</t>
+          <t>[SHONRCA12TS] SHORT SPORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -28319,16 +27569,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>RIOMIDA04TM</t>
+          <t>SHONTCA12TL</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TM] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHONTCA12TL] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -28349,16 +27599,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>RIOMIDA11TXS</t>
+          <t>SHONTCA12TM</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TXS] RIO DAMA AZUL LAVANDA</t>
+          <t>[SHONTCA12TM] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -28379,16 +27629,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>LMOFIDA31TXS</t>
+          <t>SHONTCA12TS</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>[LMOFIDA31TXS] LEGGING MOVA DAMA GRIS OSCURO</t>
+          <t>[SHONTCA12TS] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -28409,16 +27659,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>LMOFIDA31TS</t>
+          <t>SHONTCA12TXL</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>[LMOFIDA31TS] LEGGING MOVA DAMA GRIS OSCURO</t>
+          <t>[SHONTCA12TXL] EXPLORE SHORT CAB AZUL MARINO</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -28439,16 +27689,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>DAYCSTCA43TS</t>
+          <t>SHONTCA30TS</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>[DAYCSTCA43TS] DAILY CLÁSICA 3.0 CAB NEGRO</t>
+          <t>[SHONTCA30TS] EXPLORE SHORT CAB GRIS CLARO</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -28469,16 +27719,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>SHOSUCA154TS</t>
+          <t>SHONTCA31TL</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHONTCA31TL] EXPLORE SHORT CAB Gris Oscuro</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -28499,16 +27749,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>SHOSUCA154TM</t>
+          <t>SHONTCA31TXL</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHONTCA31TXL] EXPLORE SHORT CAB Gris Oscuro</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -28529,16 +27779,16 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>SHOSUCA154TL</t>
+          <t>SHONTCA33TL</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHONTCA33TL] EXPLORE SHORT  CAB KAKI</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -28559,16 +27809,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>SHOSUCA154TXL</t>
+          <t>SHONTCA43TS</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
+          <t>[SHONTCA43TS] EXPLORE SHORT CAB NEGRO</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -28589,16 +27839,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SHOSUCA156TS</t>
+          <t>SHONTCA66TL</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHONTCA66TL] EXPLORE SHORT CAB VERDE MILITAR</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -28619,16 +27869,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SHOSUCA156TM</t>
+          <t>SHOSPBFCA207TL</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -28649,16 +27899,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SHOSUCA156TL</t>
+          <t>SHOSPBFCA207TM</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -28679,16 +27929,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SHOSUCA156TXL</t>
+          <t>SHOSPBFCA207TS</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
+          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -28709,16 +27959,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SHOSUCA153TS</t>
+          <t>SHOSPBFDA207TM</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -28739,16 +27989,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SHOSUCA153TM</t>
+          <t>SHOSPBFDA207TS</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -28769,12 +28019,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SHOSUCA153TL</t>
+          <t>SHOSPBFDA207TXL</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -28799,16 +28049,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SHOSUCA153TXL</t>
+          <t>SHOSUCA153TL</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB SAL</t>
+          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -28829,16 +28079,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SHOSUCA155TS</t>
+          <t>SHOSUCA153TM</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -28859,16 +28109,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>SHOSUCA155TM</t>
+          <t>SHOSUCA153TS</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -28889,16 +28139,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>SHOSUKI155T2</t>
+          <t>SHOSUCA153TXL</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB SAL</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -28919,16 +28169,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>SHOSUKI155T1</t>
+          <t>SHOSUCA154TL</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -28949,16 +28199,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>SHOSUKI155T4</t>
+          <t>SHOSUCA154TM</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -28979,16 +28229,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>SHOSUKI155T6</t>
+          <t>SHOSUCA154TS</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
+          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -29009,16 +28259,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>SHOSUKI153T4</t>
+          <t>SHOSUCA154TXL</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB SOMBRERO</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -29039,16 +28289,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>SHOSUKI153T2</t>
+          <t>SHOSUCA155TM</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS SAL</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -29069,16 +28319,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>SHOSUKI154T1</t>
+          <t>SHOSUCA155TS</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB PLAYUELA</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -29099,16 +28349,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>SHOSUKI154T2</t>
+          <t>SHOSUCA156TL</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -29129,16 +28379,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>SHOSUKI154T4</t>
+          <t>SHOSUCA156TM</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
+          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -29159,16 +28409,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>RIOMIDA01TM</t>
+          <t>SHOSUCA156TS</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>[RIOMIDA01TM] RIO DAMA AGUAMARINA</t>
+          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -29189,16 +28439,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>VIVMIDA43TM</t>
+          <t>SHOSUCA156TXL</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>[VIVMIDA43TM] VIVI DAMA NEGRO</t>
+          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB TUCUPIDO</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -29219,16 +28469,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MARMICA43TL</t>
+          <t>SHOSUKI153T1</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>[MARMICA43TL] MAR CAB NEGRO</t>
+          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -29249,16 +28499,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>NAHFNCA24TXL</t>
+          <t>SHOSUKI153T10</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TXL] NOAH SPORT LITE CAB CORAL NEÓN</t>
+          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -29279,16 +28529,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>CLAMICA70TS</t>
+          <t>SHOSUKI153T12</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>[CLAMICA70TS] CLÁSICA CAB VINOTINTO</t>
+          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -29309,16 +28559,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>MARMICA43TS</t>
+          <t>SHOSUKI153T14</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>[MARMICA43TS] MAR CAB NEGRO</t>
+          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -29339,16 +28589,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>RIOMIDA04TXS</t>
+          <t>SHOSUKI153T2</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXS] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -29369,16 +28619,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>RIOMICA52TM</t>
+          <t>SHOSUKI153T4</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>[RIOMICA52TM] RIO CAB ROSADO NEÓN</t>
+          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -29399,16 +28649,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>SHONTCA33TL</t>
+          <t>SHOSUKI153T6</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>[SHONTCA33TL] EXPLORE SHORT  CAB KAKI</t>
+          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -29429,16 +28679,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>SHONTCA66TL</t>
+          <t>SHOSUKI153T8</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>[SHONTCA66TL] EXPLORE SHORT CAB VERDE MILITAR</t>
+          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS SAL</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -29459,16 +28709,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>SHONTCA31TXL</t>
+          <t>SHOSUKI154T1</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>[SHONTCA31TXL] EXPLORE SHORT CAB Gris Oscuro</t>
+          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -29489,16 +28739,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>SHONTCA43TS</t>
+          <t>SHOSUKI154T10</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>[SHONTCA43TS] EXPLORE SHORT CAB NEGRO</t>
+          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -29519,16 +28769,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>SHONTCA31TL</t>
+          <t>SHOSUKI154T12</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>[SHONTCA31TL] EXPLORE SHORT CAB Gris Oscuro</t>
+          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -29549,16 +28799,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MARMIKI43T14</t>
+          <t>SHOSUKI154T14</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>[MARMIKI43T14] MAR KIDS NEGRO</t>
+          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -29579,16 +28829,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>SHONTCA30TS</t>
+          <t>SHOSUKI154T2</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>[SHONTCA30TS] EXPLORE SHORT CAB GRIS CLARO</t>
+          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -29609,16 +28859,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>HELBFDA30TXS</t>
+          <t>SHOSUKI154T4</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>[HELBFDA30TXS] HELEN DAMA GRIS CLARO</t>
+          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -29639,16 +28889,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>HELBFDA30TM</t>
+          <t>SHOSUKI154T6</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>[HELBFDA30TM] HELEN DAMA GRIS CLARO</t>
+          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -29669,12 +28919,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>LMOFIDA43TM</t>
+          <t>SHOSUKI154T8</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>[LMOFIDA43TM] LEGGING MOVA DAMA NEGRO</t>
+          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS SOMBRERO</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -29699,12 +28949,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>RIOMIDA34TS</t>
+          <t>SHOSUKI155T1</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>[RIOMIDA34TS] RIO DAMA LILA</t>
+          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D480" t="n">
@@ -29729,12 +28979,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>MARMIDA34TS</t>
+          <t>SHOSUKI155T12</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>[MARMIDA34TS] MAR DAMA LILA</t>
+          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -29759,16 +29009,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>NAHFNCA24TL</t>
+          <t>SHOSUKI155T14</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TL] NOAH SPORT LITE CAB CORAL NEÓN</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -29789,16 +29039,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>VIVMIDA48TXL</t>
+          <t>SHOSUKI155T2</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>[VIVMIDA48TXL] VIVI DAMA PÚRPURA</t>
+          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -29819,16 +29069,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>MARMICA43TM</t>
+          <t>SHOSUKI155T4</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>[MARMICA43TM] MAR CAB NEGRO</t>
+          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -29849,16 +29099,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>BACCCDA158TM</t>
+          <t>SHOSUKI155T6</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>[BACCCDA158TM] BASIC LINE CROP TEE DAMA CREMA</t>
+          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -29879,16 +29129,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>BACCCDA43TS</t>
+          <t>SHOSUKI155T8</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>[BACCCDA43TS] BASIC LINE CROP TEE DAMA NEGRO</t>
+          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS PLAYUELA</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -29909,16 +29159,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>RIOMIDA04TS</t>
+          <t>SHOSUKI156T1</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TS] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -29939,16 +29189,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>RIOMICA04TM</t>
+          <t>SHOSUKI156T10</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>[RIOMICA04TM] RIO CAB AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -29969,16 +29219,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>RIOMIDA04TL</t>
+          <t>SHOSUKI156T12</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -29999,16 +29249,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>RIOMICA04TXL</t>
+          <t>SHOSUKI156T14</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -30029,16 +29279,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MARMICA04TXL</t>
+          <t>SHOSUKI156T2</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -30059,16 +29309,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>CLAMICA04TXL</t>
+          <t>SHOSUKI156T4</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>[CLAMICA04TXL] CLÁSICA CAB AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -30089,16 +29339,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MARMIDA04TL</t>
+          <t>SHOSUKI156T6</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>[MARMIDA04TL] MAR DAMA AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -30119,16 +29369,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>RIOMIDA04TM</t>
+          <t>SHOSUKI156T8</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TM] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS TUCUPIDO</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -30149,12 +29399,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>RIOMICA04TXL</t>
+          <t>SHUNTCA43T2XL</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
+          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB NEGRO</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -30179,16 +29429,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>RIOMIDA04TXS</t>
+          <t>SHUNTCA43TM</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXS] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB NEGRO</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -30209,12 +29459,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>RIOMICA04TXL</t>
+          <t>SHUNTCA43TS</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO CAB AMARILLO NEÓN</t>
+          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB NEGRO</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -30239,16 +29489,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MIAMIDA11TM</t>
+          <t>SHUNTDA43TM</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>[MIAMIDA11TM] MIA DAMA AZUL LAVANDA</t>
+          <t>[SHUNTDA43TM] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -30269,16 +29519,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>RIOMIDA01TM</t>
+          <t>SHUNTDA43TS</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>[RIOMIDA01TM] RIO DAMA AGUAMARINA</t>
+          <t>[SHUNTDA43TS] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -30299,12 +29549,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MARMICA04TXL</t>
+          <t>SHUNTDA43TXL</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>[MARMICA04TXL] MAR CAB AMARILLO NEÓN</t>
+          <t>[SHUNTDA43TXL] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -30329,16 +29579,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>RIOMIDA04TL</t>
+          <t>SHUNTDA43TXS</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[SHUNTDA43TXS] SHORT SPORT R1 DAMA NEGRO</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -30359,12 +29609,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>RIOMIDA04TXL</t>
+          <t>TALGTACA12TL</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXL] RIO DAMA AMARILLO NEÓN</t>
+          <t>[TALGTACA12TL] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="D502" t="n">
@@ -30389,16 +29639,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>RIOMICA16TM</t>
+          <t>TALGTACA12TM</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
+          <t>[TALGTACA12TM] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -30419,12 +29669,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>RIOMIDA16TS</t>
+          <t>TALGTACA12TXL</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TS] RIO DAMA BLANCO</t>
+          <t>[TALGTACA12TXL] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -30449,16 +29699,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>GEMBADA16TXS</t>
+          <t>TALGTACA12TXS</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
+          <t>[TALGTACA12TXS] TOP ALGODON CAB Azul marino</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -30479,12 +29729,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>MARMICA16T2XL</t>
+          <t>TALGTADA12TL</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>[MARMICA16T2XL] MAR CAB BLANCO</t>
+          <t>[TALGTADA12TL] TOP ALGODON DAMA Azul marino</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -30509,12 +29759,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>NAHFNCA16TL</t>
+          <t>TALGTADA12TM</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>[NAHFNCA16TL] NOAH SPORT LITE CAB BLANCO</t>
+          <t>[TALGTADA12TM] TOP ALGODON DAMA Azul marino</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -30539,12 +29789,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>RIOMICA16TS</t>
+          <t>TALGTADA12TS</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
+          <t>[TALGTADA12TS] TOP ALGODON DAMA Azul marino</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -30569,16 +29819,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>SARSPKI16T10</t>
+          <t>VIVMIDA43TM</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>[SARSPKI16T10] FALDA SARA KIDS BLANCO</t>
+          <t>[VIVMIDA43TM] VIVI DAMA NEGRO</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -30599,12 +29849,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MARMIDA16TL</t>
+          <t>VIVMIDA48TXL</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>[MARMIDA16TL] MAR DAMA BLANCO</t>
+          <t>[VIVMIDA48TXL] VIVI DAMA PÚRPURA</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -30616,1506 +29866,6 @@
         </is>
       </c>
       <c r="F510" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>MAADFDA30TM</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>[MAADFDA30TM] ADVANCE MAFE DAMA GRIS CLARO</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
-        <v>1</v>
-      </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>MARMICA04TL</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>[MARMICA04TL] MAR CAB AMARILLO NEÓN</t>
-        </is>
-      </c>
-      <c r="D512" t="n">
-        <v>2</v>
-      </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>MARMIDA34TXL</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>[MARMIDA34TXL] MAR DAMA LILA</t>
-        </is>
-      </c>
-      <c r="D513" t="n">
-        <v>1</v>
-      </c>
-      <c r="E513" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F513" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>RIOMIDA48TXS</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>[RIOMIDA48TXS] RIO DAMA PÚRPURA</t>
-        </is>
-      </c>
-      <c r="D514" t="n">
-        <v>1</v>
-      </c>
-      <c r="E514" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F514" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>RIOMIDA52TXL</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>[RIOMIDA52TXL] RIO DAMA ROSADO NEÓN</t>
-        </is>
-      </c>
-      <c r="D515" t="n">
-        <v>4</v>
-      </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>RIOMICA11T2XL</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>[RIOMICA11T2XL] RIO CAB AZUL LAVANDA</t>
-        </is>
-      </c>
-      <c r="D516" t="n">
-        <v>1</v>
-      </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>MAYFNDA16TM</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>[MAYFNDA16TM] MAYA SPORT LITE DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D517" t="n">
-        <v>1</v>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>MARMIKI52T14</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>[MARMIKI52T14] MAR KIDS ROSADO NEÓN</t>
-        </is>
-      </c>
-      <c r="D518" t="n">
-        <v>1</v>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>GEOMACADA03TL</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>[GEOMACADA03TL] GEO MAYA DAMA Amarillo</t>
-        </is>
-      </c>
-      <c r="D519" t="n">
-        <v>1</v>
-      </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>GEOMACADA03TM</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>[GEOMACADA03TM] GEO MAYA DAMA Amarillo</t>
-        </is>
-      </c>
-      <c r="D520" t="n">
-        <v>4</v>
-      </c>
-      <c r="E520" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F520" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>GEOMACADA03TS</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>[GEOMACADA03TS] GEO MAYA DAMA Amarillo</t>
-        </is>
-      </c>
-      <c r="D521" t="n">
-        <v>1</v>
-      </c>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F521" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>GEOMACADA03TXL</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>[GEOMACADA03TXL] GEO MAYA DAMA Amarillo</t>
-        </is>
-      </c>
-      <c r="D522" t="n">
-        <v>1</v>
-      </c>
-      <c r="E522" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>MAYFNDA16TM</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>[MAYFNDA16TM] MAYA SPORT LITE DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D523" t="n">
-        <v>1</v>
-      </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F523" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>DOMBFCA16TM</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>[DOMBFCA16TM] DOMINIC CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D524" t="n">
-        <v>1</v>
-      </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>GEMBADA16TL</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>[GEMBADA16TL] VESTIDO GEMMA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D525" t="n">
-        <v>1</v>
-      </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F525" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>GEMBADA16TM</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>[GEMBADA16TM] VESTIDO GEMMA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D526" t="n">
-        <v>1</v>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F526" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>MAYFNDA24TM</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>[MAYFNDA24TM] MAYA SPORT LITE DAMA CORAL NEÓN</t>
-        </is>
-      </c>
-      <c r="D527" t="n">
-        <v>1</v>
-      </c>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>MIKFNDA16TXS</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D528" t="n">
-        <v>1</v>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>SARSPKI16T10</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>[SARSPKI16T10] FALDA SARA KIDS BLANCO</t>
-        </is>
-      </c>
-      <c r="D529" t="n">
-        <v>1</v>
-      </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>CLAMIDA16TXS</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>[CLAMIDA16TXS] CLÁSICA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D530" t="n">
-        <v>1</v>
-      </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>CLAMICA04TM</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>[CLAMICA04TM] CLÁSICA CAB AMARILLO NEÓN</t>
-        </is>
-      </c>
-      <c r="D531" t="n">
-        <v>1</v>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>MAYFNDA16TXS</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>[MAYFNDA16TXS] MAYA SPORT LITE DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D532" t="n">
-        <v>1</v>
-      </c>
-      <c r="E532" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>SARSPDA16TS</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>[SARSPDA16TS] FALDA SARA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D533" t="n">
-        <v>1</v>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F533" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>GEMBADA16TXS</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>[GEMBADA16TXS] VESTIDO GEMMA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D534" t="n">
-        <v>2</v>
-      </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>SARSPDA16TXL</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>[SARSPDA16TXL] FALDA SARA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D535" t="n">
-        <v>1</v>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F535" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>RIOMICA16TXL</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TXL] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D536" t="n">
-        <v>2</v>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F536" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>RIOMICA16TM</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D537" t="n">
-        <v>1</v>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>RIOMICA16TL</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D538" t="n">
-        <v>1</v>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>RIOMICA16TS</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D539" t="n">
-        <v>1</v>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>MARMIDA16TM</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>[MARMIDA16TM] MAR DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D540" t="n">
-        <v>1</v>
-      </c>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>RIOMIDA16TXS</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>[RIOMIDA16TXS] RIO DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D541" t="n">
-        <v>2</v>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>CLAMIDA16TM</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>[CLAMIDA16TM] CLÁSICA DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D542" t="n">
-        <v>1</v>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>BAOCCCA158TM</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>[BAOCCCA158TM] BASIC LINE OVERSIZED CAB CREMA</t>
-        </is>
-      </c>
-      <c r="D543" t="n">
-        <v>1</v>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>BAOCCCA158TS</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>[BAOCCCA158TS] BASIC LINE OVERSIZED CAB CREMA</t>
-        </is>
-      </c>
-      <c r="D544" t="n">
-        <v>1</v>
-      </c>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>BACCCDA158TL</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>[BACCCDA158TL] BASIC LINE CROP TEE DAMA CREMA</t>
-        </is>
-      </c>
-      <c r="D545" t="n">
-        <v>1</v>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>RIOMICA16TS</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TS] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D546" t="n">
-        <v>2</v>
-      </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>RIOMIDA16TM</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>[RIOMIDA16TM] RIO DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D547" t="n">
-        <v>1</v>
-      </c>
-      <c r="E547" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>RIOMIDA16TL</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>[RIOMIDA16TL] RIO DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D548" t="n">
-        <v>3</v>
-      </c>
-      <c r="E548" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>RIOMICA16TM</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TM] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D549" t="n">
-        <v>3</v>
-      </c>
-      <c r="E549" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>RIOMICA16TL</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>[RIOMICA16TL] RIO CAB BLANCO</t>
-        </is>
-      </c>
-      <c r="D550" t="n">
-        <v>2</v>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>RIOMIDA16TS</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>[RIOMIDA16TS] RIO DAMA BLANCO</t>
-        </is>
-      </c>
-      <c r="D551" t="n">
-        <v>1</v>
-      </c>
-      <c r="E551" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F551" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>SHOSPBFDA207TM</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D552" t="n">
-        <v>3</v>
-      </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>SHOSPBFDA207TXL</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D553" t="n">
-        <v>8</v>
-      </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>SHOSPBFDA207TS</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D554" t="n">
-        <v>6</v>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F554" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>SHOSPBFCA207TS</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D555" t="n">
-        <v>6</v>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F555" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>SHOSPBFCA207TM</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D556" t="n">
-        <v>4</v>
-      </c>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>SHUNTCA43TS</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="D557" t="n">
-        <v>1</v>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F557" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>SHUNTCA43TM</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="D558" t="n">
-        <v>1</v>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>SHOSPBFCA207TL</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D559" t="n">
-        <v>1</v>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>DAYCSTCA43TS</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>[DAYCSTCA43TS] DAILY CLÁSICA 3.0 CAB NEGRO</t>
-        </is>
-      </c>
-      <c r="D560" t="n">
-        <v>6</v>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>TH/Posproducción</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
         <is>
           <t>map</t>
         </is>

--- a/output/Plantilla_Ajuste_Posproduccion.xlsx
+++ b/output/Plantilla_Ajuste_Posproduccion.xlsx
@@ -12,7 +12,9 @@
     <sheet name="Detalle Entrada" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Detalle Produccion" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Trazabilidad" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sin referencia Quants 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="R1 SKU corregidos Q6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sin referencia Quants 5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="R1 sin match Quants 6" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1926,7 +1928,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[MARMIDA48TS] MAR ORIGINAL DAMA (Púrpura, S)</t>
+          <t>[MARMIDA48TS] MAR ORIGINAL DAMA (S, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1956,7 +1958,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[MARMIDA50TS] MAR ORIGINAL DAMA (Rojo, S)</t>
+          <t>[MARMIDA50TS] MAR ORIGINAL DAMA (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1971,7 +1973,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>[MARMIDA53TL] MAR ORIGINAL DAMA (Rosado Pastel, L)</t>
+          <t>[MARMIDA53TL] MAR ORIGINAL DAMA (L, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1986,7 +1988,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>[MARMIDA53TXL] MAR ORIGINAL DAMA (Rosado Pastel, XL)</t>
+          <t>[MARMIDA53TXL] MAR ORIGINAL DAMA (XL, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2001,7 +2003,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>[MARMIDA66TL] MAR ORIGINAL DAMA (Verde Militar, L)</t>
+          <t>[MARMIDA66TL] MAR ORIGINAL DAMA (L, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2016,7 +2018,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>[MARMIDA66TXS] MAR ORIGINAL DAMA (Verde Militar, XS)</t>
+          <t>[MARMIDA66TXS] MAR ORIGINAL DAMA (XS, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2271,7 +2273,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>[MAYFNDA16TXL] MAYA SPORT LITE DAMA (Blanco, XL)</t>
+          <t>[MAYFNDA16TXL] MAYA SPORT LITE DAMA (XL, Blanco - White)</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2466,7 +2468,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>[NAHFNCA13TS] NOAH SPORT LITE CAB (Azul Rey, S)</t>
+          <t>[NAHFNCA13TS] NOAH SPORT LITE CAB (S, Azul Rey - Bright Royal)</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2496,7 +2498,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>[NAHFNCA16TS] NOAH SPORT LITE CAB (Blanco, S)</t>
+          <t>[NAHFNCA16TS] NOAH SPORT LITE CAB (S, Blanco - White)</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2526,7 +2528,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TM] NOAH SPORT LITE CAB (Coral Neón, M)</t>
+          <t>[NAHFNCA24TM] NOAH SPORT LITE CAB (M, Coral Neón - Neón Fire)</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -2841,7 +2843,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>[RIOMICA01T2XL] RIO ORIGINAL CAB (Aguamarina, 2XL)</t>
+          <t>[RIOMICA01T2XL] RIO ORIGINAL CAB (2XL, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -2856,7 +2858,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>[RIOMICA01TL] RIO ORIGINAL CAB (Aguamarina, L)</t>
+          <t>[RIOMICA01TL] RIO ORIGINAL CAB (L, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2871,7 +2873,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>[RIOMICA01TM] RIO ORIGINAL CAB (Aguamarina, M)</t>
+          <t>[RIOMICA01TM] RIO ORIGINAL CAB (M, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -2886,7 +2888,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>[RIOMICA01TS] RIO ORIGINAL CAB (Aguamarina, S)</t>
+          <t>[RIOMICA01TS] RIO ORIGINAL CAB (S, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2901,7 +2903,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>[RIOMICA01TXL] RIO ORIGINAL CAB (Aguamarina, XL)</t>
+          <t>[RIOMICA01TXL] RIO ORIGINAL CAB (XL, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2916,7 +2918,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>[RIOMICA04T2XL] RIO ORIGINAL CAB (Amarillo Neón, 2XL)</t>
+          <t>[RIOMICA04T2XL] RIO ORIGINAL CAB (2XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2931,7 +2933,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>[RIOMICA04TL] RIO ORIGINAL CAB (Amarillo Neón, L)</t>
+          <t>[RIOMICA04TL] RIO ORIGINAL CAB (L, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2961,7 +2963,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[RIOMICA04TS] RIO ORIGINAL CAB (Amarillo Neón, S)</t>
+          <t>[RIOMICA04TS] RIO ORIGINAL CAB (S, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3021,7 +3023,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>[RIOMICA11TM] RIO ORIGINAL CAB (Azul Lavanda, M)</t>
+          <t>[RIOMICA11TM] RIO ORIGINAL CAB (M, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3036,7 +3038,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>[RIOMICA11TS] RIO ORIGINAL CAB (Azul Lavanda, S)</t>
+          <t>[RIOMICA11TS] RIO ORIGINAL CAB (S, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3051,7 +3053,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>[RIOMICA11TXL] RIO ORIGINAL CAB (Azul Lavanda, XL)</t>
+          <t>[RIOMICA11TXL] RIO ORIGINAL CAB (XL, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3081,7 +3083,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>[RIOMICA12TL] RIO ORIGINAL CAB (Azul Marino, L)</t>
+          <t>[RIOMICA12TL] RIO ORIGINAL CAB (L, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3096,7 +3098,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>[RIOMICA12TM] RIO ORIGINAL CAB (Azul Marino, M)</t>
+          <t>[RIOMICA12TM] RIO ORIGINAL CAB (M, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3111,7 +3113,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>[RIOMICA12TS] RIO ORIGINAL CAB (Azul Marino, S)</t>
+          <t>[RIOMICA12TS] RIO ORIGINAL CAB (S, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3126,7 +3128,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>[RIOMICA12TXL] RIO ORIGINAL CAB (Azul Marino, XL)</t>
+          <t>[RIOMICA12TXL] RIO ORIGINAL CAB (XL, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3141,7 +3143,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>[RIOMICA13T2XL] RIO ORIGINAL CAB (Azul Rey, 2XL)</t>
+          <t>[RIOMICA13T2XL] RIO ORIGINAL CAB (2XL, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3156,7 +3158,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>[RIOMICA13TL] RIO ORIGINAL CAB (Azul Rey, L)</t>
+          <t>[RIOMICA13TL] RIO ORIGINAL CAB (L, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3171,7 +3173,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>[RIOMICA13TM] RIO ORIGINAL CAB (Azul Rey, M)</t>
+          <t>[RIOMICA13TM] RIO ORIGINAL CAB (M, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3186,7 +3188,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>[RIOMICA13TS] RIO ORIGINAL CAB (Azul Rey, S)</t>
+          <t>[RIOMICA13TS] RIO ORIGINAL CAB (S, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3201,7 +3203,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>[RIOMICA13TXL] RIO ORIGINAL CAB (Azul Rey, XL)</t>
+          <t>[RIOMICA13TXL] RIO ORIGINAL CAB (XL, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3336,7 +3338,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>[RIOMICA43T2XL] RIO ORIGINAL CAB (Negro, 2XL)</t>
+          <t>[RIOMICA43T2XL] RIO ORIGINAL CAB (2XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -3351,7 +3353,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>[RIOMICA43TL] RIO ORIGINAL CAB (Negro, L)</t>
+          <t>[RIOMICA43TL] RIO ORIGINAL CAB (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3366,7 +3368,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>[RIOMICA43TM] RIO ORIGINAL CAB (Negro, M)</t>
+          <t>[RIOMICA43TM] RIO ORIGINAL CAB (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3381,7 +3383,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>[RIOMICA43TS] RIO ORIGINAL CAB (Negro, S)</t>
+          <t>[RIOMICA43TS] RIO ORIGINAL CAB (S, Negro - 10)</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3396,7 +3398,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>[RIOMICA43TXL] RIO ORIGINAL CAB (Negro, XL)</t>
+          <t>[RIOMICA43TXL] RIO ORIGINAL CAB (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3411,7 +3413,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>[RIOMICA50T2XL] RIO ORIGINAL CAB (Rojo, 2XL)</t>
+          <t>[RIOMICA50T2XL] RIO ORIGINAL CAB (2XL, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -3426,7 +3428,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>[RIOMICA50TL] RIO ORIGINAL CAB (Rojo, L)</t>
+          <t>[RIOMICA50TL] RIO ORIGINAL CAB (L, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -3441,7 +3443,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>[RIOMICA50TM] RIO ORIGINAL CAB (Rojo, M)</t>
+          <t>[RIOMICA50TM] RIO ORIGINAL CAB (M, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -3456,7 +3458,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>[RIOMICA50TS] RIO ORIGINAL CAB (Rojo, S)</t>
+          <t>[RIOMICA50TS] RIO ORIGINAL CAB (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -3471,7 +3473,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>[RIOMICA50TXL] RIO ORIGINAL CAB (Rojo, XL)</t>
+          <t>[RIOMICA50TXL] RIO ORIGINAL CAB (XL, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3516,7 +3518,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>[RIOMICA66TL] RIO ORIGINAL CAB (Verde Militar, L)</t>
+          <t>[RIOMICA66TL] RIO ORIGINAL CAB (L, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -3531,7 +3533,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>[RIOMICA66TM] RIO ORIGINAL CAB (Verde Militar, M)</t>
+          <t>[RIOMICA66TM] RIO ORIGINAL CAB (M, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -3546,7 +3548,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>[RIOMICA66TS] RIO ORIGINAL CAB (Verde Militar, S)</t>
+          <t>[RIOMICA66TS] RIO ORIGINAL CAB (S, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -3561,7 +3563,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>[RIOMICA70T2XL] RIO ORIGINAL CAB (Vinotinto, 2XL)</t>
+          <t>[RIOMICA70T2XL] RIO ORIGINAL CAB (2XL, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -3576,7 +3578,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>[RIOMICA70TL] RIO ORIGINAL CAB (Vinotinto, L)</t>
+          <t>[RIOMICA70TL] RIO ORIGINAL CAB (L, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3591,7 +3593,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>[RIOMICA70TM] RIO ORIGINAL CAB (Vinotinto, M)</t>
+          <t>[RIOMICA70TM] RIO ORIGINAL CAB (M, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3726,7 +3728,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TL] RIO ORIGINAL DAMA (Azul Lavanda, L)</t>
+          <t>[RIOMIDA11TL] RIO ORIGINAL DAMA (L, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -3786,7 +3788,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TL] RIO ORIGINAL DAMA (Azul Marino, L)</t>
+          <t>[RIOMIDA12TL] RIO ORIGINAL DAMA (L, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -3801,7 +3803,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TM] RIO ORIGINAL DAMA (Azul Marino, M)</t>
+          <t>[RIOMIDA12TM] RIO ORIGINAL DAMA (M, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -3816,7 +3818,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TS] RIO ORIGINAL DAMA (Azul Marino, S)</t>
+          <t>[RIOMIDA12TS] RIO ORIGINAL DAMA (S, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -3831,7 +3833,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TXL] RIO ORIGINAL DAMA (Azul Marino, XL)</t>
+          <t>[RIOMIDA12TXL] RIO ORIGINAL DAMA (XL, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -3846,7 +3848,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TXS] RIO ORIGINAL DAMA (Azul Marino, XS)</t>
+          <t>[RIOMIDA12TXS] RIO ORIGINAL DAMA (XS, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -3906,7 +3908,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXL] RIO ORIGINAL DAMA (Blanco, XL)</t>
+          <t>[RIOMIDA16TXL] RIO ORIGINAL DAMA (XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -3966,7 +3968,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TL] RIO ORIGINAL DAMA (Negro, L)</t>
+          <t>[RIOMIDA43TL] RIO ORIGINAL DAMA (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -3981,7 +3983,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TM] RIO ORIGINAL DAMA (Negro, M)</t>
+          <t>[RIOMIDA43TM] RIO ORIGINAL DAMA (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -3996,7 +3998,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TXL] RIO ORIGINAL DAMA (Negro, XL)</t>
+          <t>[RIOMIDA43TXL] RIO ORIGINAL DAMA (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4011,7 +4013,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TXS] RIO ORIGINAL DAMA (Negro, XS)</t>
+          <t>[RIOMIDA43TXS] RIO ORIGINAL DAMA (XS, Negro - 10)</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4026,7 +4028,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TL] RIO ORIGINAL DAMA (Púrpura, L)</t>
+          <t>[RIOMIDA48TL] RIO ORIGINAL DAMA (L, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4056,7 +4058,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TS] RIO ORIGINAL DAMA (Púrpura, S)</t>
+          <t>[RIOMIDA48TS] RIO ORIGINAL DAMA (S, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -4071,7 +4073,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TXL] RIO ORIGINAL DAMA (Púrpura, XL)</t>
+          <t>[RIOMIDA48TXL] RIO ORIGINAL DAMA (XL, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -4101,7 +4103,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>[RIOMIDA50TS] RIO ORIGINAL DAMA (Rojo, S)</t>
+          <t>[RIOMIDA50TS] RIO ORIGINAL DAMA (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -4146,7 +4148,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TL] RIO ORIGINAL DAMA (Rosado Pastel, L)</t>
+          <t>[RIOMIDA53TL] RIO ORIGINAL DAMA (L, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4161,7 +4163,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TM] RIO ORIGINAL DAMA (Rosado Pastel, M)</t>
+          <t>[RIOMIDA53TM] RIO ORIGINAL DAMA (M, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -4176,7 +4178,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TS] RIO ORIGINAL DAMA (Rosado Pastel, S)</t>
+          <t>[RIOMIDA53TS] RIO ORIGINAL DAMA (S, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -4191,7 +4193,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TXL] RIO ORIGINAL DAMA (Rosado Pastel, XL)</t>
+          <t>[RIOMIDA53TXL] RIO ORIGINAL DAMA (XL, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4206,7 +4208,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TXS] RIO ORIGINAL DAMA (Rosado Pastel, XS)</t>
+          <t>[RIOMIDA53TXS] RIO ORIGINAL DAMA (XS, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -4236,7 +4238,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TM] RIO ORIGINAL DAMA (Verde Militar, M)</t>
+          <t>[RIOMIDA66TM] RIO ORIGINAL DAMA (M, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4251,7 +4253,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TS] RIO ORIGINAL DAMA (Verde Militar, S)</t>
+          <t>[RIOMIDA66TS] RIO ORIGINAL DAMA (S, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -4281,7 +4283,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXS] RIO ORIGINAL DAMA (Verde Militar, XS)</t>
+          <t>[RIOMIDA66TXS] RIO ORIGINAL DAMA (XS, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -4311,7 +4313,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>[RIOMIDA70TXS] RIO ORIGINAL DAMA (Vinotinto, XS)</t>
+          <t>[RIOMIDA70TXS] RIO ORIGINAL DAMA (XS, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -4371,7 +4373,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>[RIOMIKI16T14] RIO ORIGINAL KIDS (Blanco, 14)</t>
+          <t>[RIOMIKI16T14] RIO ORIGINAL KIDS (14, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -4476,7 +4478,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>[SARSPDA16TXS] FALDA SARA DAMA (Blanco, XS)</t>
+          <t>[SARSPDA16TXS] FALDA SARA DAMA (XS, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -5016,7 +5018,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>[SHONTDA12TM] EXPLORE SHORT DAMA (Azul Marino, M)</t>
+          <t>[SHONTDA12TM] EXPLORE SHORT DAMA (M, Azul Marino - 586)</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -5091,11 +5093,11 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB (SAL, L)</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -5106,11 +5108,11 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -5121,11 +5123,11 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -5136,11 +5138,11 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB (SAL, XL)</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -5151,11 +5153,11 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, L)</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -5166,11 +5168,11 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, M)</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -5181,11 +5183,11 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB (SAL, L)</t>
+          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, S)</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -5196,11 +5198,11 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
+          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, XL)</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -5211,11 +5213,11 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
+          <t>[SHOSUCA155T2XL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, 2XL)</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -5226,11 +5228,11 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB (SAL, XL)</t>
+          <t>[SHOSUCA155TL] SHORT PLAYA ESTAMPADO CAB (L, PLAYUELA)</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -5241,11 +5243,11 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, L)</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -5256,11 +5258,11 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, M)</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -5271,11 +5273,11 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, S)</t>
+          <t>[SHOSUCA155TXL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, XL)</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -5286,11 +5288,11 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, XL)</t>
+          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, L)</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -5301,11 +5303,11 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>[SHOSUCA155T2XL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, 2XL)</t>
+          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, M)</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -5316,11 +5318,11 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, L)</t>
+          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, S)</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -5331,11 +5333,11 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
+          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, XL)</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -5346,11 +5348,11 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
+          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS (SAL, 10)</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -5361,11 +5363,11 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TXL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, XL)</t>
+          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS (SAL, 12)</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -5376,11 +5378,11 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, L)</t>
+          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS (SAL, 14)</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -5391,11 +5393,11 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, M)</t>
+          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS (SAL, 1)</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -5406,11 +5408,11 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, S)</t>
+          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS (SAL, 2)</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -5421,11 +5423,11 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, XL)</t>
+          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS (SAL, 4)</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5436,11 +5438,11 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS (SAL, 10)</t>
+          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS (SAL, 6)</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -5451,11 +5453,11 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS (SAL, 12)</t>
+          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS (SAL, 8)</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -5466,11 +5468,11 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS (SAL, 14)</t>
+          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 10)</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -5481,11 +5483,11 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS (SAL, 1)</t>
+          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 12)</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -5496,11 +5498,11 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS (SAL, 2)</t>
+          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 14)</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -5511,11 +5513,11 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS (SAL, 4)</t>
+          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 1)</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -5526,7 +5528,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS (SAL, 6)</t>
+          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 2)</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -5541,11 +5543,11 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS (SAL, 8)</t>
+          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 4)</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -5556,11 +5558,11 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 10)</t>
+          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 6)</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -5571,11 +5573,11 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 12)</t>
+          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 8)</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -5586,11 +5588,11 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 14)</t>
+          <t>[SHOSUKI155T10] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 10)</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -5601,11 +5603,11 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 1)</t>
+          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 12)</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -5616,11 +5618,11 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 2)</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -5631,7 +5633,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 4)</t>
+          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 1)</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -5646,11 +5648,11 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 6)</t>
+          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 2)</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -5661,11 +5663,11 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 8)</t>
+          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 4)</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -5676,11 +5678,11 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T10] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 10)</t>
+          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 6)</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -5691,7 +5693,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 12)</t>
+          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 8)</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -5706,11 +5708,11 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
+          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 10)</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -5721,11 +5723,11 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 1)</t>
+          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 12)</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -5736,11 +5738,11 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 2)</t>
+          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 14)</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -5751,11 +5753,11 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 4)</t>
+          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 1)</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -5766,11 +5768,11 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 6)</t>
+          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 2)</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -5781,11 +5783,11 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 8)</t>
+          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 4)</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -5796,7 +5798,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 10)</t>
+          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 6)</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -5811,11 +5813,11 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 12)</t>
+          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 8)</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -5826,11 +5828,11 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 14)</t>
+          <t>[SHOUNKI69T4] SHORT PLAYA KIDS (4, Verde Pino - 195920)</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -5841,11 +5843,11 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 1)</t>
+          <t>[SHR2VICA43TL] SHORT R2 CAB (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -5856,11 +5858,11 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 2)</t>
+          <t>[SHR2VICA43TM] SHORT R2 CAB (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -5871,11 +5873,11 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 4)</t>
+          <t>[SHR2VICA43TS] SHORT R2 CAB (S, Negro - 10)</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -5886,11 +5888,11 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 6)</t>
+          <t>[SHR2VICA43TXL] SHORT R2 CAB (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -5901,11 +5903,11 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 8)</t>
+          <t>[SHR2VICA70TXL] SHORT R2 CAB (XL, Vinotinto - 47)</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -5916,11 +5918,11 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>[SHOUNKI69T4] SHORT PLAYA KIDS (Verde Pino, 4)</t>
+          <t>[SHR2VIDA123TL] SHORT R2 DAMA (L, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -5931,7 +5933,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TL] SHORT R2 CAB (Negro, L)</t>
+          <t>[SHR2VIDA123TM] SHORT R2 DAMA (M, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -5946,7 +5948,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TM] SHORT R2 CAB (Negro, M)</t>
+          <t>[SHR2VIDA123TS] SHORT R2 DAMA (S, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -5961,11 +5963,11 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TS] SHORT R2 CAB (Negro, S)</t>
+          <t>[SHR2VIDA123TXS] SHORT R2 DAMA (XS, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -5976,11 +5978,11 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TXL] SHORT R2 CAB (Negro, XL)</t>
+          <t>[SHR2VIDA13TL] SHORT R2 DAMA (L, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -5991,7 +5993,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>[SHR2VICA70TXL] SHORT R2 CAB (Vinotinto, XL)</t>
+          <t>[SHR2VIDA13TM] SHORT R2 DAMA (M, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -6006,11 +6008,11 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TL] SHORT R2 DAMA (Verde Manzana, L)</t>
+          <t>[SHR2VIDA13TS] SHORT R2 DAMA (S, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -6021,11 +6023,11 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TM] SHORT R2 DAMA (Verde Manzana, M)</t>
+          <t>[SHR2VIDA13TXS] SHORT R2 DAMA (XS, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -6036,11 +6038,11 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TS] SHORT R2 DAMA (Verde Manzana, S)</t>
+          <t>[SHR2VIDA43TL] SHORT R2 DAMA (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -6051,11 +6053,11 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TXS] SHORT R2 DAMA (Verde Manzana, XS)</t>
+          <t>[SHR2VIDA43TM] SHORT R2 DAMA (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -6066,11 +6068,11 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TL] SHORT R2 DAMA (Azul Rey, L)</t>
+          <t>[SHR2VIDA43TS] SHORT R2 DAMA (S, Negro - 10)</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -6081,11 +6083,11 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TM] SHORT R2 DAMA (Azul Rey, M)</t>
+          <t>[SHR2VIDA43TXS] SHORT R2 DAMA (XS, Negro - 10)</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -6096,11 +6098,11 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TS] SHORT R2 DAMA (Azul Rey, S)</t>
+          <t>[SHUNTCA157TS] SHORT SPORT R1 CAB (Gris, S)</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -6111,11 +6113,11 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TXS] SHORT R2 DAMA (Azul Rey, XS)</t>
+          <t>[SHUNTCA31TL] SHORT SPORT R1 CAB (Gris Oscuro, L)</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -6126,11 +6128,11 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TL] SHORT R2 DAMA (Negro, L)</t>
+          <t>[SHUNTCA31TS] SHORT SPORT R1 CAB (Gris Oscuro, S)</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -6141,11 +6143,11 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TM] SHORT R2 DAMA (Negro, M)</t>
+          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB (Negro, 2XL)</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -6156,11 +6158,11 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TS] SHORT R2 DAMA (Negro, S)</t>
+          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB (Negro, M)</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -6171,11 +6173,11 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TXS] SHORT R2 DAMA (Negro, XS)</t>
+          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB (Negro, S)</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -6186,11 +6188,11 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB (Negro, 2XL)</t>
+          <t>[SHUNTCA43TXL] SHORT SPORT R1 CAB (Negro, XL)</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -6201,11 +6203,11 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB (Negro, M)</t>
+          <t>[SHUNTDA157TM] SHORT SPORT R1 DAMA (Gris, M)</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -6216,11 +6218,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB (Negro, S)</t>
+          <t>[SHUNTDA157TS] SHORT SPORT R1 DAMA (Gris, S)</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6231,11 +6233,11 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TXL] SHORT SPORT R1 CAB (Negro, XL)</t>
+          <t>[SHUNTDA157TXL] SHORT SPORT R1 DAMA (Gris, XL)</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -6246,7 +6248,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>[SHUNTDA157TXS] SHORT SPORT R1 DAMA (Gris, XS)</t>
+          <t>[SHUNTDA157TXS] SHORT SPORT R1 DAMA (XS, Gris - 9672)</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -6711,7 +6713,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>[TMOFIDA09TL] TOP MOVA (Azul Cielo, L)</t>
+          <t>[TMOFIDA09TL] TOP MOVA (Azul Cielo - Frozen, L)</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -6726,7 +6728,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>[TMOFIDA09TS] TOP MOVA (Azul Cielo, S)</t>
+          <t>[TMOFIDA09TS] TOP MOVA (Azul Cielo - Frozen, S)</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -6862,7 +6864,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[MARMIDA48TS] MAR ORIGINAL DAMA (Púrpura, S)</t>
+          <t>[MARMIDA48TS] MAR ORIGINAL DAMA (S, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -6877,7 +6879,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[MARMIDA50TS] MAR ORIGINAL DAMA (Rojo, S)</t>
+          <t>[MARMIDA50TS] MAR ORIGINAL DAMA (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6892,7 +6894,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[MARMIDA53TL] MAR ORIGINAL DAMA (Rosado Pastel, L)</t>
+          <t>[MARMIDA53TL] MAR ORIGINAL DAMA (L, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6907,7 +6909,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[MARMIDA53TXL] MAR ORIGINAL DAMA (Rosado Pastel, XL)</t>
+          <t>[MARMIDA53TXL] MAR ORIGINAL DAMA (XL, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6922,7 +6924,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[MARMIDA66TL] MAR ORIGINAL DAMA (Verde Militar, L)</t>
+          <t>[MARMIDA66TL] MAR ORIGINAL DAMA (L, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6937,7 +6939,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[MARMIDA66TXS] MAR ORIGINAL DAMA (Verde Militar, XS)</t>
+          <t>[MARMIDA66TXS] MAR ORIGINAL DAMA (XS, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6952,7 +6954,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[MAYFNDA16TXL] MAYA SPORT LITE DAMA (Blanco, XL)</t>
+          <t>[MAYFNDA16TXL] MAYA SPORT LITE DAMA (XL, Blanco - White)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6967,7 +6969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA (Blanco, XS)</t>
+          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA (XS, Blanco - White)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6982,7 +6984,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[NAHFNCA13TS] NOAH SPORT LITE CAB (Azul Rey, S)</t>
+          <t>[NAHFNCA13TS] NOAH SPORT LITE CAB (S, Azul Rey - Bright Royal)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6997,7 +6999,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[NAHFNCA16TS] NOAH SPORT LITE CAB (Blanco, S)</t>
+          <t>[NAHFNCA16TS] NOAH SPORT LITE CAB (S, Blanco - White)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7012,7 +7014,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TM] NOAH SPORT LITE CAB (Coral Neón, M)</t>
+          <t>[NAHFNCA24TM] NOAH SPORT LITE CAB (M, Coral Neón - Neón Fire)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7027,7 +7029,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[RIOMICA01T2XL] RIO ORIGINAL CAB (Aguamarina, 2XL)</t>
+          <t>[RIOMICA01T2XL] RIO ORIGINAL CAB (2XL, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7042,7 +7044,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[RIOMICA01TL] RIO ORIGINAL CAB (Aguamarina, L)</t>
+          <t>[RIOMICA01TL] RIO ORIGINAL CAB (L, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7057,7 +7059,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[RIOMICA01TM] RIO ORIGINAL CAB (Aguamarina, M)</t>
+          <t>[RIOMICA01TM] RIO ORIGINAL CAB (M, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7072,7 +7074,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[RIOMICA01TS] RIO ORIGINAL CAB (Aguamarina, S)</t>
+          <t>[RIOMICA01TS] RIO ORIGINAL CAB (S, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -7087,7 +7089,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[RIOMICA01TXL] RIO ORIGINAL CAB (Aguamarina, XL)</t>
+          <t>[RIOMICA01TXL] RIO ORIGINAL CAB (XL, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -7102,7 +7104,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[RIOMICA04T2XL] RIO ORIGINAL CAB (Amarillo Neón, 2XL)</t>
+          <t>[RIOMICA04T2XL] RIO ORIGINAL CAB (2XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7117,7 +7119,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[RIOMICA04TL] RIO ORIGINAL CAB (Amarillo Neón, L)</t>
+          <t>[RIOMICA04TL] RIO ORIGINAL CAB (L, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -7132,7 +7134,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[RIOMICA04TM] RIO ORIGINAL CAB (Amarillo Neón, M)</t>
+          <t>[RIOMICA04TM] RIO ORIGINAL CAB (M, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -7147,7 +7149,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[RIOMICA04TS] RIO ORIGINAL CAB (Amarillo Neón, S)</t>
+          <t>[RIOMICA04TS] RIO ORIGINAL CAB (S, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7162,7 +7164,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO ORIGINAL CAB (Amarillo Neón, XL)</t>
+          <t>[RIOMICA04TXL] RIO ORIGINAL CAB (XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -7177,7 +7179,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[RIOMICA11T2XL] RIO ORIGINAL CAB (Azul Lavanda, 2XL)</t>
+          <t>[RIOMICA11T2XL] RIO ORIGINAL CAB (2XL, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7192,7 +7194,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[RIOMICA11TM] RIO ORIGINAL CAB (Azul Lavanda, M)</t>
+          <t>[RIOMICA11TM] RIO ORIGINAL CAB (M, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7207,7 +7209,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[RIOMICA11TS] RIO ORIGINAL CAB (Azul Lavanda, S)</t>
+          <t>[RIOMICA11TS] RIO ORIGINAL CAB (S, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7222,7 +7224,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[RIOMICA11TXL] RIO ORIGINAL CAB (Azul Lavanda, XL)</t>
+          <t>[RIOMICA11TXL] RIO ORIGINAL CAB (XL, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7252,7 +7254,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[RIOMICA12TL] RIO ORIGINAL CAB (Azul Marino, L)</t>
+          <t>[RIOMICA12TL] RIO ORIGINAL CAB (L, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7267,7 +7269,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[RIOMICA12TM] RIO ORIGINAL CAB (Azul Marino, M)</t>
+          <t>[RIOMICA12TM] RIO ORIGINAL CAB (M, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -7282,7 +7284,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[RIOMICA12TS] RIO ORIGINAL CAB (Azul Marino, S)</t>
+          <t>[RIOMICA12TS] RIO ORIGINAL CAB (S, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7297,7 +7299,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[RIOMICA12TXL] RIO ORIGINAL CAB (Azul Marino, XL)</t>
+          <t>[RIOMICA12TXL] RIO ORIGINAL CAB (XL, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7312,7 +7314,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[RIOMICA13T2XL] RIO ORIGINAL CAB (Azul Rey, 2XL)</t>
+          <t>[RIOMICA13T2XL] RIO ORIGINAL CAB (2XL, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -7327,7 +7329,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[RIOMICA13TL] RIO ORIGINAL CAB (Azul Rey, L)</t>
+          <t>[RIOMICA13TL] RIO ORIGINAL CAB (L, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -7342,7 +7344,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[RIOMICA13TM] RIO ORIGINAL CAB (Azul Rey, M)</t>
+          <t>[RIOMICA13TM] RIO ORIGINAL CAB (M, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7357,7 +7359,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[RIOMICA13TS] RIO ORIGINAL CAB (Azul Rey, S)</t>
+          <t>[RIOMICA13TS] RIO ORIGINAL CAB (S, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -7372,7 +7374,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[RIOMICA13TXL] RIO ORIGINAL CAB (Azul Rey, XL)</t>
+          <t>[RIOMICA13TXL] RIO ORIGINAL CAB (XL, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -7387,7 +7389,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[RIOMICA16T2XL] RIO ORIGINAL CAB (Blanco, 2XL)</t>
+          <t>[RIOMICA16T2XL] RIO ORIGINAL CAB (2XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7402,7 +7404,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[RIOMICA16TL] RIO ORIGINAL CAB (Blanco, L)</t>
+          <t>[RIOMICA16TL] RIO ORIGINAL CAB (L, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7417,7 +7419,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[RIOMICA16TM] RIO ORIGINAL CAB (Blanco, M)</t>
+          <t>[RIOMICA16TM] RIO ORIGINAL CAB (M, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7432,7 +7434,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO ORIGINAL CAB (Blanco, S)</t>
+          <t>[RIOMICA16TS] RIO ORIGINAL CAB (S, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -7447,7 +7449,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[RIOMICA16TXL] RIO ORIGINAL CAB (Blanco, XL)</t>
+          <t>[RIOMICA16TXL] RIO ORIGINAL CAB (XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7462,7 +7464,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[RIOMICA43T2XL] RIO ORIGINAL CAB (Negro, 2XL)</t>
+          <t>[RIOMICA43T2XL] RIO ORIGINAL CAB (2XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -7477,7 +7479,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[RIOMICA43TL] RIO ORIGINAL CAB (Negro, L)</t>
+          <t>[RIOMICA43TL] RIO ORIGINAL CAB (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7492,7 +7494,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[RIOMICA43TM] RIO ORIGINAL CAB (Negro, M)</t>
+          <t>[RIOMICA43TM] RIO ORIGINAL CAB (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7507,7 +7509,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[RIOMICA43TS] RIO ORIGINAL CAB (Negro, S)</t>
+          <t>[RIOMICA43TS] RIO ORIGINAL CAB (S, Negro - 10)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7522,7 +7524,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[RIOMICA43TXL] RIO ORIGINAL CAB (Negro, XL)</t>
+          <t>[RIOMICA43TXL] RIO ORIGINAL CAB (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7537,7 +7539,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[RIOMICA50T2XL] RIO ORIGINAL CAB (Rojo, 2XL)</t>
+          <t>[RIOMICA50T2XL] RIO ORIGINAL CAB (2XL, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7552,7 +7554,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[RIOMICA50TL] RIO ORIGINAL CAB (Rojo, L)</t>
+          <t>[RIOMICA50TL] RIO ORIGINAL CAB (L, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -7567,7 +7569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[RIOMICA50TM] RIO ORIGINAL CAB (Rojo, M)</t>
+          <t>[RIOMICA50TM] RIO ORIGINAL CAB (M, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7582,7 +7584,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[RIOMICA50TS] RIO ORIGINAL CAB (Rojo, S)</t>
+          <t>[RIOMICA50TS] RIO ORIGINAL CAB (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7597,7 +7599,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[RIOMICA50TXL] RIO ORIGINAL CAB (Rojo, XL)</t>
+          <t>[RIOMICA50TXL] RIO ORIGINAL CAB (XL, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7612,7 +7614,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[RIOMICA66TL] RIO ORIGINAL CAB (Verde Militar, L)</t>
+          <t>[RIOMICA66TL] RIO ORIGINAL CAB (L, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7627,7 +7629,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[RIOMICA66TM] RIO ORIGINAL CAB (Verde Militar, M)</t>
+          <t>[RIOMICA66TM] RIO ORIGINAL CAB (M, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7642,7 +7644,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[RIOMICA66TS] RIO ORIGINAL CAB (Verde Militar, S)</t>
+          <t>[RIOMICA66TS] RIO ORIGINAL CAB (S, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7657,7 +7659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[RIOMICA70T2XL] RIO ORIGINAL CAB (Vinotinto, 2XL)</t>
+          <t>[RIOMICA70T2XL] RIO ORIGINAL CAB (2XL, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -7672,7 +7674,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[RIOMICA70TL] RIO ORIGINAL CAB (Vinotinto, L)</t>
+          <t>[RIOMICA70TL] RIO ORIGINAL CAB (L, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7687,7 +7689,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[RIOMICA70TM] RIO ORIGINAL CAB (Vinotinto, M)</t>
+          <t>[RIOMICA70TM] RIO ORIGINAL CAB (M, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7702,7 +7704,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[RIOMICA70TXL] RIO ORIGINAL CAB (Vinotinto, XL)</t>
+          <t>[RIOMICA70TXL] RIO ORIGINAL CAB (XL, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -7717,7 +7719,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TL] RIO ORIGINAL DAMA (Amarillo Neón, L)</t>
+          <t>[RIOMIDA04TL] RIO ORIGINAL DAMA (L, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -7732,7 +7734,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TM] RIO ORIGINAL DAMA (Amarillo Neón, M)</t>
+          <t>[RIOMIDA04TM] RIO ORIGINAL DAMA (M, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -7747,7 +7749,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TS] RIO ORIGINAL DAMA (Amarillo Neón, S)</t>
+          <t>[RIOMIDA04TS] RIO ORIGINAL DAMA (S, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -7762,7 +7764,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXL] RIO ORIGINAL DAMA (Amarillo Neón, XL)</t>
+          <t>[RIOMIDA04TXL] RIO ORIGINAL DAMA (XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -7777,7 +7779,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXS] RIO ORIGINAL DAMA (Amarillo Neón, XS)</t>
+          <t>[RIOMIDA04TXS] RIO ORIGINAL DAMA (XS, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -7792,7 +7794,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TL] RIO ORIGINAL DAMA (Azul Lavanda, L)</t>
+          <t>[RIOMIDA11TL] RIO ORIGINAL DAMA (L, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7807,7 +7809,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TXS] RIO ORIGINAL DAMA (Azul Lavanda, XS)</t>
+          <t>[RIOMIDA11TXS] RIO ORIGINAL DAMA (XS, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -7822,7 +7824,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TL] RIO ORIGINAL DAMA (Azul Marino, L)</t>
+          <t>[RIOMIDA12TL] RIO ORIGINAL DAMA (L, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7837,7 +7839,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TM] RIO ORIGINAL DAMA (Azul Marino, M)</t>
+          <t>[RIOMIDA12TM] RIO ORIGINAL DAMA (M, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -7852,7 +7854,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TS] RIO ORIGINAL DAMA (Azul Marino, S)</t>
+          <t>[RIOMIDA12TS] RIO ORIGINAL DAMA (S, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -7867,7 +7869,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TXL] RIO ORIGINAL DAMA (Azul Marino, XL)</t>
+          <t>[RIOMIDA12TXL] RIO ORIGINAL DAMA (XL, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -7882,7 +7884,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TXS] RIO ORIGINAL DAMA (Azul Marino, XS)</t>
+          <t>[RIOMIDA12TXS] RIO ORIGINAL DAMA (XS, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -7897,7 +7899,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TL] RIO ORIGINAL DAMA (Blanco, L)</t>
+          <t>[RIOMIDA16TL] RIO ORIGINAL DAMA (L, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -7912,7 +7914,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXL] RIO ORIGINAL DAMA (Blanco, XL)</t>
+          <t>[RIOMIDA16TXL] RIO ORIGINAL DAMA (XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -7927,7 +7929,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXS] RIO ORIGINAL DAMA (Blanco, XS)</t>
+          <t>[RIOMIDA16TXS] RIO ORIGINAL DAMA (XS, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -7957,7 +7959,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TL] RIO ORIGINAL DAMA (Negro, L)</t>
+          <t>[RIOMIDA43TL] RIO ORIGINAL DAMA (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -7972,7 +7974,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TM] RIO ORIGINAL DAMA (Negro, M)</t>
+          <t>[RIOMIDA43TM] RIO ORIGINAL DAMA (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -7987,7 +7989,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TXL] RIO ORIGINAL DAMA (Negro, XL)</t>
+          <t>[RIOMIDA43TXL] RIO ORIGINAL DAMA (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -8002,7 +8004,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TXS] RIO ORIGINAL DAMA (Negro, XS)</t>
+          <t>[RIOMIDA43TXS] RIO ORIGINAL DAMA (XS, Negro - 10)</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -8017,7 +8019,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TL] RIO ORIGINAL DAMA (Púrpura, L)</t>
+          <t>[RIOMIDA48TL] RIO ORIGINAL DAMA (L, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -8032,7 +8034,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TS] RIO ORIGINAL DAMA (Púrpura, S)</t>
+          <t>[RIOMIDA48TS] RIO ORIGINAL DAMA (S, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8047,7 +8049,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TXL] RIO ORIGINAL DAMA (Púrpura, XL)</t>
+          <t>[RIOMIDA48TXL] RIO ORIGINAL DAMA (XL, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8062,7 +8064,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TXS] RIO ORIGINAL DAMA (Púrpura, XS)</t>
+          <t>[RIOMIDA48TXS] RIO ORIGINAL DAMA (XS, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -8077,7 +8079,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[RIOMIDA50TS] RIO ORIGINAL DAMA (Rojo, S)</t>
+          <t>[RIOMIDA50TS] RIO ORIGINAL DAMA (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -8092,7 +8094,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TL] RIO ORIGINAL DAMA (Rosado Pastel, L)</t>
+          <t>[RIOMIDA53TL] RIO ORIGINAL DAMA (L, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -8107,7 +8109,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TM] RIO ORIGINAL DAMA (Rosado Pastel, M)</t>
+          <t>[RIOMIDA53TM] RIO ORIGINAL DAMA (M, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -8122,7 +8124,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TS] RIO ORIGINAL DAMA (Rosado Pastel, S)</t>
+          <t>[RIOMIDA53TS] RIO ORIGINAL DAMA (S, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -8137,7 +8139,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TXL] RIO ORIGINAL DAMA (Rosado Pastel, XL)</t>
+          <t>[RIOMIDA53TXL] RIO ORIGINAL DAMA (XL, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -8152,7 +8154,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TXS] RIO ORIGINAL DAMA (Rosado Pastel, XS)</t>
+          <t>[RIOMIDA53TXS] RIO ORIGINAL DAMA (XS, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -8167,7 +8169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TM] RIO ORIGINAL DAMA (Verde Militar, M)</t>
+          <t>[RIOMIDA66TM] RIO ORIGINAL DAMA (M, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -8182,7 +8184,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TS] RIO ORIGINAL DAMA (Verde Militar, S)</t>
+          <t>[RIOMIDA66TS] RIO ORIGINAL DAMA (S, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -8197,7 +8199,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXL] RIO ORIGINAL DAMA (Verde Militar, XL)</t>
+          <t>[RIOMIDA66TXL] RIO ORIGINAL DAMA (XL, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -8212,7 +8214,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXS] RIO ORIGINAL DAMA (Verde Militar, XS)</t>
+          <t>[RIOMIDA66TXS] RIO ORIGINAL DAMA (XS, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -8227,7 +8229,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[RIOMIDA70TXS] RIO ORIGINAL DAMA (Vinotinto, XS)</t>
+          <t>[RIOMIDA70TXS] RIO ORIGINAL DAMA (XS, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -8242,7 +8244,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[RIOMIKI16T14] RIO ORIGINAL KIDS (Blanco, 14)</t>
+          <t>[RIOMIKI16T14] RIO ORIGINAL KIDS (14, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -8257,7 +8259,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[SARSPDA16TXS] FALDA SARA DAMA (Blanco, XS)</t>
+          <t>[SARSPDA16TXS] FALDA SARA DAMA (XS, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -8272,7 +8274,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[SHONTDA12TM] EXPLORE SHORT DAMA (Azul Marino, M)</t>
+          <t>[SHONTDA12TM] EXPLORE SHORT DAMA (M, Azul Marino - 586)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -8287,7 +8289,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (M, SAL)</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -8302,7 +8304,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (S, SAL)</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -8317,7 +8319,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, L)</t>
+          <t>[SHOSUCA155TL] SHORT PLAYA ESTAMPADO CAB (L, PLAYUELA)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -8332,7 +8334,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (M, PLAYUELA)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -8347,7 +8349,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (S, PLAYUELA)</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -8362,7 +8364,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (14, PLAYUELA)</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -8377,7 +8379,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[SHOUNKI69T4] SHORT PLAYA KIDS (Verde Pino, 4)</t>
+          <t>[SHOUNKI69T4] SHORT PLAYA KIDS (4, Verde Pino - 195920)</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -8392,7 +8394,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TL] SHORT R2 CAB (Negro, L)</t>
+          <t>[SHR2VICA43TL] SHORT R2 CAB (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -8407,7 +8409,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TM] SHORT R2 CAB (Negro, M)</t>
+          <t>[SHR2VICA43TM] SHORT R2 CAB (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -8422,7 +8424,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TS] SHORT R2 CAB (Negro, S)</t>
+          <t>[SHR2VICA43TS] SHORT R2 CAB (S, Negro - 10)</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -8437,7 +8439,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TXL] SHORT R2 CAB (Negro, XL)</t>
+          <t>[SHR2VICA43TXL] SHORT R2 CAB (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -8452,7 +8454,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>[SHR2VICA70TXL] SHORT R2 CAB (Vinotinto, XL)</t>
+          <t>[SHR2VICA70TXL] SHORT R2 CAB (XL, Vinotinto - 47)</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -8467,7 +8469,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TL] SHORT R2 DAMA (Verde Manzana, L)</t>
+          <t>[SHR2VIDA123TL] SHORT R2 DAMA (L, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -8482,7 +8484,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TM] SHORT R2 DAMA (Verde Manzana, M)</t>
+          <t>[SHR2VIDA123TM] SHORT R2 DAMA (M, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -8497,7 +8499,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TS] SHORT R2 DAMA (Verde Manzana, S)</t>
+          <t>[SHR2VIDA123TS] SHORT R2 DAMA (S, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -8512,7 +8514,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TXS] SHORT R2 DAMA (Verde Manzana, XS)</t>
+          <t>[SHR2VIDA123TXS] SHORT R2 DAMA (XS, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -8527,7 +8529,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TL] SHORT R2 DAMA (Azul Rey, L)</t>
+          <t>[SHR2VIDA13TL] SHORT R2 DAMA (L, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8542,7 +8544,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TM] SHORT R2 DAMA (Azul Rey, M)</t>
+          <t>[SHR2VIDA13TM] SHORT R2 DAMA (M, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -8557,7 +8559,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TS] SHORT R2 DAMA (Azul Rey, S)</t>
+          <t>[SHR2VIDA13TS] SHORT R2 DAMA (S, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -8572,7 +8574,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TXS] SHORT R2 DAMA (Azul Rey, XS)</t>
+          <t>[SHR2VIDA13TXS] SHORT R2 DAMA (XS, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -8587,7 +8589,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TL] SHORT R2 DAMA (Negro, L)</t>
+          <t>[SHR2VIDA43TL] SHORT R2 DAMA (L, Negro - 10)</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -8602,7 +8604,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TM] SHORT R2 DAMA (Negro, M)</t>
+          <t>[SHR2VIDA43TM] SHORT R2 DAMA (M, Negro - 10)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -8617,7 +8619,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TS] SHORT R2 DAMA (Negro, S)</t>
+          <t>[SHR2VIDA43TS] SHORT R2 DAMA (S, Negro - 10)</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -8632,7 +8634,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TXS] SHORT R2 DAMA (Negro, XS)</t>
+          <t>[SHR2VIDA43TXS] SHORT R2 DAMA (XS, Negro - 10)</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -8647,7 +8649,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>[SHUNTDA157TXS] SHORT SPORT R1 DAMA (Gris, XS)</t>
+          <t>[SHUNTDA157TXS] SHORT SPORT R1 DAMA (XS, Gris - 9672)</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -8692,7 +8694,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>[TMOFIDA09TL] TOP MOVA (Azul Cielo, L)</t>
+          <t>[TMOFIDA09TL] TOP MOVA (Azul Cielo - Frozen, L)</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -8707,7 +8709,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>[TMOFIDA09TS] TOP MOVA (Azul Cielo, S)</t>
+          <t>[TMOFIDA09TS] TOP MOVA (Azul Cielo - Frozen, S)</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -13554,11 +13556,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB (SAL, L)</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13569,11 +13571,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13584,11 +13586,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13599,11 +13601,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB (SAL, XL)</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13614,11 +13616,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, L)</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13629,11 +13631,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, M)</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13644,11 +13646,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB (SAL, L)</t>
+          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, S)</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -13659,11 +13661,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
+          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, XL)</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -13674,11 +13676,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -13689,11 +13691,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB (SAL, XL)</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -13704,11 +13706,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, L)</t>
+          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, L)</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -13719,11 +13721,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, M)</t>
+          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, M)</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -13734,11 +13736,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, S)</t>
+          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, S)</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -13749,11 +13751,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, XL)</t>
+          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, XL)</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -13764,11 +13766,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
+          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS (SAL, 10)</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -13779,11 +13781,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
+          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS (SAL, 12)</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -13794,11 +13796,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, L)</t>
+          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS (SAL, 14)</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -13809,11 +13811,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, M)</t>
+          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS (SAL, 1)</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -13824,11 +13826,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, S)</t>
+          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS (SAL, 2)</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -13839,11 +13841,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, XL)</t>
+          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS (SAL, 4)</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -13854,11 +13856,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS (SAL, 10)</t>
+          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS (SAL, 6)</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -13869,11 +13871,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS (SAL, 12)</t>
+          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS (SAL, 8)</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -13884,11 +13886,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS (SAL, 14)</t>
+          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 10)</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -13899,11 +13901,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS (SAL, 1)</t>
+          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 12)</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -13914,11 +13916,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS (SAL, 2)</t>
+          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 14)</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -13929,11 +13931,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS (SAL, 4)</t>
+          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 1)</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -13944,11 +13946,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS (SAL, 6)</t>
+          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 2)</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -13959,11 +13961,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS (SAL, 8)</t>
+          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 4)</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -13974,11 +13976,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 10)</t>
+          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 6)</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -13989,11 +13991,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 12)</t>
+          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 8)</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -14004,11 +14006,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 14)</t>
+          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 12)</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -14019,11 +14021,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 1)</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -14034,11 +14036,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 2)</t>
+          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 1)</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -14049,11 +14051,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 4)</t>
+          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 2)</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -14064,11 +14066,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 6)</t>
+          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 4)</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -14079,11 +14081,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 8)</t>
+          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 6)</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -14094,7 +14096,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 12)</t>
+          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 8)</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -14109,7 +14111,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
+          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 10)</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -14124,11 +14126,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 1)</t>
+          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 12)</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -14139,11 +14141,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 2)</t>
+          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 14)</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -14154,7 +14156,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 4)</t>
+          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 1)</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -14169,11 +14171,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 6)</t>
+          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 2)</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -14184,11 +14186,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 8)</t>
+          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 4)</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -14199,11 +14201,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 10)</t>
+          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 6)</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -14214,11 +14216,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 12)</t>
+          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 8)</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -14229,11 +14231,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 14)</t>
+          <t>[SHUNTCA157TS] SHORT SPORT R1 CAB (Gris, S)</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -14244,11 +14246,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 1)</t>
+          <t>[SHUNTCA31TL] SHORT SPORT R1 CAB (Gris Oscuro, L)</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -14259,11 +14261,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 2)</t>
+          <t>[SHUNTCA31TS] SHORT SPORT R1 CAB (Gris Oscuro, S)</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -14274,11 +14276,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 4)</t>
+          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB (Negro, 2XL)</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -14289,11 +14291,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 6)</t>
+          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB (Negro, M)</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -14304,11 +14306,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 8)</t>
+          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB (Negro, S)</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -14319,11 +14321,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB (Negro, 2XL)</t>
+          <t>[SHUNTDA157TM] SHORT SPORT R1 DAMA (Gris, M)</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -14334,11 +14336,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB (Negro, M)</t>
+          <t>[SHUNTDA157TS] SHORT SPORT R1 DAMA (Gris, S)</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -14349,11 +14351,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB (Negro, S)</t>
+          <t>[SHUNTDA157TXL] SHORT SPORT R1 DAMA (Gris, XL)</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -14615,7 +14617,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[RIOMICA13TM] RIO ORIGINAL CAB (Azul Rey, M)</t>
+          <t>[RIOMICA13TM] RIO ORIGINAL CAB (M, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -14628,7 +14630,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14645,7 +14647,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[RIOMICA13TS] RIO ORIGINAL CAB (Azul Rey, S)</t>
+          <t>[RIOMICA13TS] RIO ORIGINAL CAB (S, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -14658,7 +14660,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14677,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[RIOMICA13TXL] RIO ORIGINAL CAB (Azul Rey, XL)</t>
+          <t>[RIOMICA13TXL] RIO ORIGINAL CAB (XL, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -14688,7 +14690,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14707,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[RIOMICA13TL] RIO ORIGINAL CAB (Azul Rey, L)</t>
+          <t>[RIOMICA13TL] RIO ORIGINAL CAB (L, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -14718,7 +14720,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14735,7 +14737,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[RIOMICA43TM] RIO ORIGINAL CAB (Negro, M)</t>
+          <t>[RIOMICA43TM] RIO ORIGINAL CAB (M, Negro - 10)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -14748,7 +14750,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14767,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[RIOMICA43TS] RIO ORIGINAL CAB (Negro, S)</t>
+          <t>[RIOMICA43TS] RIO ORIGINAL CAB (S, Negro - 10)</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -14778,7 +14780,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14795,7 +14797,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[RIOMICA43TL] RIO ORIGINAL CAB (Negro, L)</t>
+          <t>[RIOMICA43TL] RIO ORIGINAL CAB (L, Negro - 10)</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -14808,7 +14810,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14827,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[RIOMICA12TS] RIO ORIGINAL CAB (Azul Marino, S)</t>
+          <t>[RIOMICA12TS] RIO ORIGINAL CAB (S, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -14838,7 +14840,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14855,7 +14857,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[RIOMICA12TL] RIO ORIGINAL CAB (Azul Marino, L)</t>
+          <t>[RIOMICA12TL] RIO ORIGINAL CAB (L, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -14868,7 +14870,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14885,7 +14887,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[RIOMICA12TM] RIO ORIGINAL CAB (Azul Marino, M)</t>
+          <t>[RIOMICA12TM] RIO ORIGINAL CAB (M, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -14898,7 +14900,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14915,7 +14917,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[RIOMICA43TXL] RIO ORIGINAL CAB (Negro, XL)</t>
+          <t>[RIOMICA43TXL] RIO ORIGINAL CAB (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -14928,7 +14930,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14945,7 +14947,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[RIOMICA16TXL] RIO ORIGINAL CAB (Blanco, XL)</t>
+          <t>[RIOMICA16TXL] RIO ORIGINAL CAB (XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -14958,7 +14960,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -14975,7 +14977,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[RIOMICA16TM] RIO ORIGINAL CAB (Blanco, M)</t>
+          <t>[RIOMICA16TM] RIO ORIGINAL CAB (M, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -14988,7 +14990,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15007,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[RIOMICA70TM] RIO ORIGINAL CAB (Vinotinto, M)</t>
+          <t>[RIOMICA70TM] RIO ORIGINAL CAB (M, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -15018,7 +15020,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15037,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[RIOMICA70TL] RIO ORIGINAL CAB (Vinotinto, L)</t>
+          <t>[RIOMICA70TL] RIO ORIGINAL CAB (L, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -15048,7 +15050,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15067,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[RIOMICA16TL] RIO ORIGINAL CAB (Blanco, L)</t>
+          <t>[RIOMICA16TL] RIO ORIGINAL CAB (L, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -15078,7 +15080,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15097,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[RIOMICA16TS] RIO ORIGINAL CAB (Blanco, S)</t>
+          <t>[RIOMICA16TS] RIO ORIGINAL CAB (S, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -15108,7 +15110,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15127,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[RIOMICA12TXL] RIO ORIGINAL CAB (Azul Marino, XL)</t>
+          <t>[RIOMICA12TXL] RIO ORIGINAL CAB (XL, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -15138,7 +15140,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15155,7 +15157,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[RIOMICA11TS] RIO ORIGINAL CAB (Azul Lavanda, S)</t>
+          <t>[RIOMICA11TS] RIO ORIGINAL CAB (S, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -15168,7 +15170,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15187,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[RIOMICA11TM] RIO ORIGINAL CAB (Azul Lavanda, M)</t>
+          <t>[RIOMICA11TM] RIO ORIGINAL CAB (M, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -15198,7 +15200,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15215,7 +15217,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[RIOMICA11TXL] RIO ORIGINAL CAB (Azul Lavanda, XL)</t>
+          <t>[RIOMICA11TXL] RIO ORIGINAL CAB (XL, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -15228,7 +15230,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15247,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[RIOMICA70TXL] RIO ORIGINAL CAB (Vinotinto, XL)</t>
+          <t>[RIOMICA70TXL] RIO ORIGINAL CAB (XL, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -15258,7 +15260,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15277,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[MARMIDA66TL] MAR ORIGINAL DAMA (Verde Militar, L)</t>
+          <t>[MARMIDA66TL] MAR ORIGINAL DAMA (L, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -15288,7 +15290,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15307,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[RIOMICA50TL] RIO ORIGINAL CAB (Rojo, L)</t>
+          <t>[RIOMICA50TL] RIO ORIGINAL CAB (L, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -15318,7 +15320,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15337,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[RIOMICA66TM] RIO ORIGINAL CAB (Verde Militar, M)</t>
+          <t>[RIOMICA66TM] RIO ORIGINAL CAB (M, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -15348,7 +15350,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15367,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[RIOMICA13T2XL] RIO ORIGINAL CAB (Azul Rey, 2XL)</t>
+          <t>[RIOMICA13T2XL] RIO ORIGINAL CAB (2XL, Azul Rey - 50122)</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -15378,7 +15380,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15397,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[RIOMICA50TXL] RIO ORIGINAL CAB (Rojo, XL)</t>
+          <t>[RIOMICA50TXL] RIO ORIGINAL CAB (XL, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -15408,7 +15410,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15427,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[RIOMICA66TL] RIO ORIGINAL CAB (Verde Militar, L)</t>
+          <t>[RIOMICA66TL] RIO ORIGINAL CAB (L, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -15438,7 +15440,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15455,7 +15457,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[RIOMICA66TS] RIO ORIGINAL CAB (Verde Militar, S)</t>
+          <t>[RIOMICA66TS] RIO ORIGINAL CAB (S, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -15468,7 +15470,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15487,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[RIOMICA50TS] RIO ORIGINAL CAB (Rojo, S)</t>
+          <t>[RIOMICA50TS] RIO ORIGINAL CAB (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -15498,7 +15500,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15517,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[RIOMICA50TM] RIO ORIGINAL CAB (Rojo, M)</t>
+          <t>[RIOMICA50TM] RIO ORIGINAL CAB (M, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -15528,7 +15530,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15547,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TL] SHORT R2 CAB (Negro, L)</t>
+          <t>[SHR2VICA43TL] SHORT R2 CAB (L, Negro - 10)</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -15558,7 +15560,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15577,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TS] SHORT R2 CAB (Negro, S)</t>
+          <t>[SHR2VICA43TS] SHORT R2 CAB (S, Negro - 10)</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -15588,7 +15590,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15607,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TXL] SHORT R2 CAB (Negro, XL)</t>
+          <t>[SHR2VICA43TXL] SHORT R2 CAB (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -15618,7 +15620,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15635,7 +15637,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TS] SHORT R2 DAMA (Verde Manzana, S)</t>
+          <t>[SHR2VIDA123TS] SHORT R2 DAMA (S, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -15648,7 +15650,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15667,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TM] SHORT R2 DAMA (Verde Manzana, M)</t>
+          <t>[SHR2VIDA123TM] SHORT R2 DAMA (M, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -15678,7 +15680,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15697,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TM] SHORT R2 DAMA (Azul Rey, M)</t>
+          <t>[SHR2VIDA13TM] SHORT R2 DAMA (M, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -15708,7 +15710,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15727,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TS] SHORT R2 DAMA (Negro, S)</t>
+          <t>[SHR2VIDA43TS] SHORT R2 DAMA (S, Negro - 10)</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -15738,7 +15740,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15755,7 +15757,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TM] SHORT R2 DAMA (Negro, M)</t>
+          <t>[SHR2VIDA43TM] SHORT R2 DAMA (M, Negro - 10)</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -15768,7 +15770,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15787,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[SHR2VICA70TXL] SHORT R2 CAB (Vinotinto, XL)</t>
+          <t>[SHR2VICA70TXL] SHORT R2 CAB (XL, Vinotinto - 47)</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -15798,7 +15800,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15815,7 +15817,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[SHR2VICA43TM] SHORT R2 CAB (Negro, M)</t>
+          <t>[SHR2VICA43TM] SHORT R2 CAB (M, Negro - 10)</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -15828,7 +15830,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15845,7 +15847,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TS] SHORT R2 DAMA (Azul Rey, S)</t>
+          <t>[SHR2VIDA13TS] SHORT R2 DAMA (S, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -15858,7 +15860,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15877,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TXS] RIO ORIGINAL DAMA (Negro, XS)</t>
+          <t>[RIOMIDA43TXS] RIO ORIGINAL DAMA (XS, Negro - 10)</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -15888,7 +15890,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15907,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TM] RIO ORIGINAL DAMA (Negro, M)</t>
+          <t>[RIOMIDA43TM] RIO ORIGINAL DAMA (M, Negro - 10)</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -15918,7 +15920,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15937,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TS] RIO ORIGINAL DAMA (Azul Marino, S)</t>
+          <t>[RIOMIDA12TS] RIO ORIGINAL DAMA (S, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -15948,7 +15950,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15965,7 +15967,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TXS] RIO ORIGINAL DAMA (Azul Marino, XS)</t>
+          <t>[RIOMIDA12TXS] RIO ORIGINAL DAMA (XS, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -15978,7 +15980,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TM] RIO ORIGINAL DAMA (Azul Marino, M)</t>
+          <t>[RIOMIDA12TM] RIO ORIGINAL DAMA (M, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -16008,7 +16010,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16027,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[MARMIDA53TL] MAR ORIGINAL DAMA (Rosado Pastel, L)</t>
+          <t>[MARMIDA53TL] MAR ORIGINAL DAMA (L, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -16038,7 +16040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16055,7 +16057,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[RIOMICA01TS] RIO ORIGINAL CAB (Aguamarina, S)</t>
+          <t>[RIOMICA01TS] RIO ORIGINAL CAB (S, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -16068,7 +16070,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16087,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[RIOMICA04TS] RIO ORIGINAL CAB (Amarillo Neón, S)</t>
+          <t>[RIOMICA04TS] RIO ORIGINAL CAB (S, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -16098,7 +16100,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16117,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[RIOMICA01TM] RIO ORIGINAL CAB (Aguamarina, M)</t>
+          <t>[RIOMICA01TM] RIO ORIGINAL CAB (M, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -16128,7 +16130,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16147,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[RIOMICA01TL] RIO ORIGINAL CAB (Aguamarina, L)</t>
+          <t>[RIOMICA01TL] RIO ORIGINAL CAB (L, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -16158,7 +16160,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16177,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[RIOMICA01TXL] RIO ORIGINAL CAB (Aguamarina, XL)</t>
+          <t>[RIOMICA01TXL] RIO ORIGINAL CAB (XL, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -16188,7 +16190,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16207,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[RIOMICA43T2XL] RIO ORIGINAL CAB (Negro, 2XL)</t>
+          <t>[RIOMICA43T2XL] RIO ORIGINAL CAB (2XL, Negro - 10)</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -16218,7 +16220,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16235,7 +16237,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[RIOMICA04TXL] RIO ORIGINAL CAB (Amarillo Neón, XL)</t>
+          <t>[RIOMICA04TXL] RIO ORIGINAL CAB (XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -16248,7 +16250,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16297,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[RIOMICA04TL] RIO ORIGINAL CAB (Amarillo Neón, L)</t>
+          <t>[RIOMICA04TL] RIO ORIGINAL CAB (L, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -16308,7 +16310,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16327,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[RIOMICA04TM] RIO ORIGINAL CAB (Amarillo Neón, M)</t>
+          <t>[RIOMICA04TM] RIO ORIGINAL CAB (M, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -16338,7 +16340,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16357,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXS] RIO ORIGINAL DAMA (Blanco, XS)</t>
+          <t>[RIOMIDA16TXS] RIO ORIGINAL DAMA (XS, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -16368,7 +16370,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16385,7 +16387,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[RIOMICA16T2XL] RIO ORIGINAL CAB (Blanco, 2XL)</t>
+          <t>[RIOMICA16T2XL] RIO ORIGINAL CAB (2XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -16398,7 +16400,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16415,7 +16417,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[RIOMICA11T2XL] RIO ORIGINAL CAB (Azul Lavanda, 2XL)</t>
+          <t>[RIOMICA11T2XL] RIO ORIGINAL CAB (2XL, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -16428,7 +16430,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16447,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[RIOMICA70T2XL] RIO ORIGINAL CAB (Vinotinto, 2XL)</t>
+          <t>[RIOMICA70T2XL] RIO ORIGINAL CAB (2XL, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -16458,7 +16460,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16477,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[MARMIDA48TS] MAR ORIGINAL DAMA (Púrpura, S)</t>
+          <t>[MARMIDA48TS] MAR ORIGINAL DAMA (S, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -16488,7 +16490,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16507,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TL] SHORT R2 DAMA (Negro, L)</t>
+          <t>[SHR2VIDA43TL] SHORT R2 DAMA (L, Negro - 10)</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -16518,7 +16520,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16535,7 +16537,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TL] SHORT R2 DAMA (Azul Rey, L)</t>
+          <t>[SHR2VIDA13TL] SHORT R2 DAMA (L, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -16548,7 +16550,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16567,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[SHR2VIDA13TXS] SHORT R2 DAMA (Azul Rey, XS)</t>
+          <t>[SHR2VIDA13TXS] SHORT R2 DAMA (XS, Azul Rey - 5535)</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -16578,7 +16580,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16597,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TL] SHORT R2 DAMA (Verde Manzana, L)</t>
+          <t>[SHR2VIDA123TL] SHORT R2 DAMA (L, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -16608,7 +16610,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16627,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[SHR2VIDA123TXS] SHORT R2 DAMA (Verde Manzana, XS)</t>
+          <t>[SHR2VIDA123TXS] SHORT R2 DAMA (XS, Verde Manzana - 61458)</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -16638,7 +16640,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16657,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TM] RIO ORIGINAL DAMA (Verde Militar, M)</t>
+          <t>[RIOMIDA66TM] RIO ORIGINAL DAMA (M, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -16668,7 +16670,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16687,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TXS] RIO ORIGINAL DAMA (Púrpura, XS)</t>
+          <t>[RIOMIDA48TXS] RIO ORIGINAL DAMA (XS, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -16698,7 +16700,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16715,7 +16717,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXS] RIO ORIGINAL DAMA (Verde Militar, XS)</t>
+          <t>[RIOMIDA66TXS] RIO ORIGINAL DAMA (XS, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -16728,7 +16730,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16747,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TS] RIO ORIGINAL DAMA (Verde Militar, S)</t>
+          <t>[RIOMIDA66TS] RIO ORIGINAL DAMA (S, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -16758,7 +16760,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16775,7 +16777,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TS] RIO ORIGINAL DAMA (Púrpura, S)</t>
+          <t>[RIOMIDA48TS] RIO ORIGINAL DAMA (S, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -16788,7 +16790,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16807,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[RIOMICA50T2XL] RIO ORIGINAL CAB (Rojo, 2XL)</t>
+          <t>[RIOMICA50T2XL] RIO ORIGINAL CAB (2XL, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -16818,7 +16820,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16835,7 +16837,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TXS] RIO ORIGINAL DAMA (Azul Lavanda, XS)</t>
+          <t>[RIOMIDA11TXS] RIO ORIGINAL DAMA (XS, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -16848,7 +16850,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16867,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TL] RIO ORIGINAL DAMA (Negro, L)</t>
+          <t>[RIOMIDA43TL] RIO ORIGINAL DAMA (L, Negro - 10)</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -16878,7 +16880,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16897,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[SHR2VIDA43TXS] SHORT R2 DAMA (Negro, XS)</t>
+          <t>[SHR2VIDA43TXS] SHORT R2 DAMA (XS, Negro - 10)</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -16908,7 +16910,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16925,7 +16927,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[RIOMIDA43TXL] RIO ORIGINAL DAMA (Negro, XL)</t>
+          <t>[RIOMIDA43TXL] RIO ORIGINAL DAMA (XL, Negro - 10)</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -16938,7 +16940,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16957,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TL] RIO ORIGINAL DAMA (Azul Marino, L)</t>
+          <t>[RIOMIDA12TL] RIO ORIGINAL DAMA (L, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -16968,7 +16970,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -16985,7 +16987,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TS] RIO ORIGINAL DAMA (Amarillo Neón, S)</t>
+          <t>[RIOMIDA04TS] RIO ORIGINAL DAMA (S, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -16998,7 +17000,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17017,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TM] RIO ORIGINAL DAMA (Amarillo Neón, M)</t>
+          <t>[RIOMIDA04TM] RIO ORIGINAL DAMA (M, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -17028,7 +17030,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17045,7 +17047,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[SHOUNKI69T4] SHORT PLAYA KIDS (Verde Pino, 4)</t>
+          <t>[SHOUNKI69T4] SHORT PLAYA KIDS (4, Verde Pino - 195920)</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -17058,7 +17060,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17075,7 +17077,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[RIOMIDA12TXL] RIO ORIGINAL DAMA (Azul Marino, XL)</t>
+          <t>[RIOMIDA12TXL] RIO ORIGINAL DAMA (XL, Azul Marino - 5102)</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -17088,7 +17090,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17105,7 +17107,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXS] RIO ORIGINAL DAMA (Amarillo Neón, XS)</t>
+          <t>[RIOMIDA04TXS] RIO ORIGINAL DAMA (XS, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -17118,7 +17120,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17137,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TXL] RIO ORIGINAL DAMA (Blanco, XL)</t>
+          <t>[RIOMIDA16TXL] RIO ORIGINAL DAMA (XL, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -17148,7 +17150,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17167,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[RIOMICA04T2XL] RIO ORIGINAL CAB (Amarillo Neón, 2XL)</t>
+          <t>[RIOMICA04T2XL] RIO ORIGINAL CAB (2XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -17178,7 +17180,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17195,7 +17197,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[RIOMICA01T2XL] RIO ORIGINAL CAB (Aguamarina, 2XL)</t>
+          <t>[RIOMICA01T2XL] RIO ORIGINAL CAB (2XL, Aguamarina - 61275)</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -17208,7 +17210,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17227,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[RIOMIDA16TL] RIO ORIGINAL DAMA (Blanco, L)</t>
+          <t>[RIOMIDA16TL] RIO ORIGINAL DAMA (L, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -17238,7 +17240,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17257,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TM] RIO ORIGINAL DAMA (Rosado Pastel, M)</t>
+          <t>[RIOMIDA53TM] RIO ORIGINAL DAMA (M, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -17268,7 +17270,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17285,7 +17287,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TS] RIO ORIGINAL DAMA (Rosado Pastel, S)</t>
+          <t>[RIOMIDA53TS] RIO ORIGINAL DAMA (S, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -17298,7 +17300,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17317,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TXS] RIO ORIGINAL DAMA (Rosado Pastel, XS)</t>
+          <t>[RIOMIDA53TXS] RIO ORIGINAL DAMA (XS, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -17328,7 +17330,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17347,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TXL] RIO ORIGINAL DAMA (Púrpura, XL)</t>
+          <t>[RIOMIDA48TXL] RIO ORIGINAL DAMA (XL, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -17358,7 +17360,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17377,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[RIOMIDA48TL] RIO ORIGINAL DAMA (Púrpura, L)</t>
+          <t>[RIOMIDA48TL] RIO ORIGINAL DAMA (L, Púrpura - 4223)</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -17388,7 +17390,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17405,7 +17407,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[RIOMIDA11TL] RIO ORIGINAL DAMA (Azul Lavanda, L)</t>
+          <t>[RIOMIDA11TL] RIO ORIGINAL DAMA (L, Azul Lavanda - 5300)</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -17418,7 +17420,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17435,7 +17437,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (M, PLAYUELA)</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -17448,7 +17450,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17465,7 +17467,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>[SHUNTDA157TXS] SHORT SPORT R1 DAMA (Gris, XS)</t>
+          <t>[SHUNTDA157TXS] SHORT SPORT R1 DAMA (XS, Gris - 9672)</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -17478,7 +17480,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17497,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TL] RIO ORIGINAL DAMA (Amarillo Neón, L)</t>
+          <t>[RIOMIDA04TL] RIO ORIGINAL DAMA (L, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -17508,7 +17510,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17538,7 +17540,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17555,7 +17557,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>[RIOMIDA04TXL] RIO ORIGINAL DAMA (Amarillo Neón, XL)</t>
+          <t>[RIOMIDA04TXL] RIO ORIGINAL DAMA (XL, Amarillo Neón - 60281)</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -17568,7 +17570,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17587,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TL] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, L)</t>
+          <t>[SHOSUCA155TL] SHORT PLAYA ESTAMPADO CAB (L, PLAYUELA)</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -17598,7 +17600,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17617,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TL] RIO ORIGINAL DAMA (Rosado Pastel, L)</t>
+          <t>[RIOMIDA53TL] RIO ORIGINAL DAMA (L, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -17628,7 +17630,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17645,7 +17647,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>[RIOMIDA53TXL] RIO ORIGINAL DAMA (Rosado Pastel, XL)</t>
+          <t>[RIOMIDA53TXL] RIO ORIGINAL DAMA (XL, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -17658,7 +17660,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17677,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[SHONTDA12TM] EXPLORE SHORT DAMA (Azul Marino, M)</t>
+          <t>[SHONTDA12TM] EXPLORE SHORT DAMA (M, Azul Marino - 586)</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -17688,7 +17690,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17718,7 +17720,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17735,7 +17737,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>[TMOFIDA09TS] TOP MOVA (Azul Cielo, S)</t>
+          <t>[TMOFIDA09TS] TOP MOVA (Azul Cielo - Frozen, S)</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -17748,7 +17750,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17765,7 +17767,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[SARSPDA16TXS] FALDA SARA DAMA (Blanco, XS)</t>
+          <t>[SARSPDA16TXS] FALDA SARA DAMA (XS, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -17778,7 +17780,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17795,7 +17797,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (S, PLAYUELA)</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -17808,7 +17810,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17825,7 +17827,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[TMOFIDA09TL] TOP MOVA (Azul Cielo, L)</t>
+          <t>[TMOFIDA09TL] TOP MOVA (Azul Cielo - Frozen, L)</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -17838,7 +17840,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17857,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>[NAHFNCA13TS] NOAH SPORT LITE CAB (Azul Rey, S)</t>
+          <t>[NAHFNCA13TS] NOAH SPORT LITE CAB (S, Azul Rey - Bright Royal)</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -17868,7 +17870,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17885,7 +17887,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>[MARMIDA66TXS] MAR ORIGINAL DAMA (Verde Militar, XS)</t>
+          <t>[MARMIDA66TXS] MAR ORIGINAL DAMA (XS, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -17898,7 +17900,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17915,7 +17917,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[MAYFNDA16TXL] MAYA SPORT LITE DAMA (Blanco, XL)</t>
+          <t>[MAYFNDA16TXL] MAYA SPORT LITE DAMA (XL, Blanco - White)</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -17928,7 +17930,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17947,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[NAHFNCA24TM] NOAH SPORT LITE CAB (Coral Neón, M)</t>
+          <t>[NAHFNCA24TM] NOAH SPORT LITE CAB (M, Coral Neón - Neón Fire)</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -17958,7 +17960,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -17975,7 +17977,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[MARMIDA50TS] MAR ORIGINAL DAMA (Rojo, S)</t>
+          <t>[MARMIDA50TS] MAR ORIGINAL DAMA (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -17988,7 +17990,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18007,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[MARMIDA53TXL] MAR ORIGINAL DAMA (Rosado Pastel, XL)</t>
+          <t>[MARMIDA53TXL] MAR ORIGINAL DAMA (XL, Rosado Pastel - 20663)</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -18018,7 +18020,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18035,7 +18037,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA (Blanco, XS)</t>
+          <t>[MIKFNDA16TXS] MIKA SPORT LITE DAMA (XS, Blanco - White)</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -18048,7 +18050,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18065,7 +18067,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>[NAHFNCA16TS] NOAH SPORT LITE CAB (Blanco, S)</t>
+          <t>[NAHFNCA16TS] NOAH SPORT LITE CAB (S, Blanco - White)</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -18078,7 +18080,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18097,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (14, PLAYUELA)</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -18108,7 +18110,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18125,7 +18127,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>[RIOMIDA70TXS] RIO ORIGINAL DAMA (Vinotinto, XS)</t>
+          <t>[RIOMIDA70TXS] RIO ORIGINAL DAMA (XS, Vinotinto - 4717)</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -18138,7 +18140,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18155,7 +18157,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>[RIOMIDA66TXL] RIO ORIGINAL DAMA (Verde Militar, XL)</t>
+          <t>[RIOMIDA66TXL] RIO ORIGINAL DAMA (XL, Verde Militar - 60620)</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -18168,7 +18170,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18217,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (M, SAL)</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -18228,7 +18230,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18245,7 +18247,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>[RIOMIKI16T14] RIO ORIGINAL KIDS (Blanco, 14)</t>
+          <t>[RIOMIKI16T14] RIO ORIGINAL KIDS (14, Blanco - 1259j)</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -18258,7 +18260,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18277,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (S, SAL)</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -18288,7 +18290,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18307,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>[RIOMIDA50TS] RIO ORIGINAL DAMA (Rojo, S)</t>
+          <t>[RIOMIDA50TS] RIO ORIGINAL DAMA (S, Rojo - 3392)</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -18318,7 +18320,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>provided</t>
         </is>
       </c>
     </row>
@@ -27870,16 +27872,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SHOSPBFCA207TL</t>
+          <t>SHOSUCA153TL</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB (SAL, L)</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -27888,7 +27890,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>quants_master</t>
         </is>
       </c>
     </row>
@@ -27900,16 +27902,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SHOSPBFCA207TM</t>
+          <t>SHOSUCA153TM</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -27918,7 +27920,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>quants_master</t>
         </is>
       </c>
     </row>
@@ -27930,16 +27932,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SHOSPBFCA207TS</t>
+          <t>SHOSUCA153TS</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -27948,7 +27950,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>quants_master</t>
         </is>
       </c>
     </row>
@@ -27960,16 +27962,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SHOSPBFDA207TM</t>
+          <t>SHOSUCA153TXL</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB (SAL, XL)</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -27978,7 +27980,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>quants_master</t>
         </is>
       </c>
     </row>
@@ -27990,16 +27992,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SHOSPBFDA207TS</t>
+          <t>SHOSUCA154TL</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, L)</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -28008,7 +28010,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>quants_master</t>
         </is>
       </c>
     </row>
@@ -28020,16 +28022,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SHOSPBFDA207TXL</t>
+          <t>SHOSUCA154TM</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
+          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, M)</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
@@ -28038,7 +28040,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>quants_master</t>
         </is>
       </c>
     </row>
@@ -28050,16 +28052,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SHOSUCA153TL</t>
+          <t>SHOSUCA154TS</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TL] SHORT PLAYA ESTAMPADO CAB (SAL, L)</t>
+          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, S)</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -28080,16 +28082,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SHOSUCA153TM</t>
+          <t>SHOSUCA154TXL</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TM] SHORT PLAYA ESTAMPADO CAB (SAL, M)</t>
+          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, XL)</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -28110,16 +28112,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>SHOSUCA153TS</t>
+          <t>SHOSUCA155TM</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TS] SHORT PLAYA ESTAMPADO CAB (SAL, S)</t>
+          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -28140,16 +28142,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>SHOSUCA153TXL</t>
+          <t>SHOSUCA155TS</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>[SHOSUCA153TXL] SHORT PLAYA ESTAMPADO CAB (SAL, XL)</t>
+          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -28170,16 +28172,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>SHOSUCA154TL</t>
+          <t>SHOSUCA156TL</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, L)</t>
+          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, L)</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -28200,16 +28202,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>SHOSUCA154TM</t>
+          <t>SHOSUCA156TM</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TM] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, M)</t>
+          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, M)</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -28230,16 +28232,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>SHOSUCA154TS</t>
+          <t>SHOSUCA156TS</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TS] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, S)</t>
+          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, S)</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -28260,16 +28262,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>SHOSUCA154TXL</t>
+          <t>SHOSUCA156TXL</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>[SHOSUCA154TXL] SHORT PLAYA ESTAMPADO CAB (SOMBRERO, XL)</t>
+          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, XL)</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -28290,16 +28292,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>SHOSUCA155TM</t>
+          <t>SHOSUKI153T1</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TM] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, M)</t>
+          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS (SAL, 1)</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -28320,16 +28322,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>SHOSUCA155TS</t>
+          <t>SHOSUKI153T10</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>[SHOSUCA155TS] SHORT PLAYA ESTAMPADO CAB (PLAYUELA, S)</t>
+          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS (SAL, 10)</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -28350,16 +28352,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>SHOSUCA156TL</t>
+          <t>SHOSUKI153T12</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, L)</t>
+          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS (SAL, 12)</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -28380,16 +28382,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>SHOSUCA156TM</t>
+          <t>SHOSUKI153T14</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TM] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, M)</t>
+          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS (SAL, 14)</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -28410,16 +28412,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>SHOSUCA156TS</t>
+          <t>SHOSUKI153T2</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TS] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, S)</t>
+          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS (SAL, 2)</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -28440,16 +28442,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SHOSUCA156TXL</t>
+          <t>SHOSUKI153T4</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>[SHOSUCA156TXL] SHORT PLAYA ESTAMPADO CAB (TUCUPIDO, XL)</t>
+          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS (SAL, 4)</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -28470,16 +28472,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>SHOSUKI153T1</t>
+          <t>SHOSUKI153T6</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T1] SHORT PLAYA ESTAMPADO KIDS (SAL, 1)</t>
+          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS (SAL, 6)</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -28500,16 +28502,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SHOSUKI153T10</t>
+          <t>SHOSUKI153T8</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T10] SHORT PLAYA ESTAMPADO KIDS (SAL, 10)</t>
+          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS (SAL, 8)</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -28530,16 +28532,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SHOSUKI153T12</t>
+          <t>SHOSUKI154T1</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T12] SHORT PLAYA ESTAMPADO KIDS (SAL, 12)</t>
+          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 1)</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -28560,16 +28562,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>SHOSUKI153T14</t>
+          <t>SHOSUKI154T10</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T14] SHORT PLAYA ESTAMPADO KIDS (SAL, 14)</t>
+          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 10)</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -28590,12 +28592,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>SHOSUKI153T2</t>
+          <t>SHOSUKI154T12</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T2] SHORT PLAYA ESTAMPADO KIDS (SAL, 2)</t>
+          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 12)</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -28620,16 +28622,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>SHOSUKI153T4</t>
+          <t>SHOSUKI154T14</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T4] SHORT PLAYA ESTAMPADO KIDS (SAL, 4)</t>
+          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 14)</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -28650,16 +28652,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>SHOSUKI153T6</t>
+          <t>SHOSUKI154T2</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T6] SHORT PLAYA ESTAMPADO KIDS (SAL, 6)</t>
+          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 2)</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -28680,16 +28682,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>SHOSUKI153T8</t>
+          <t>SHOSUKI154T4</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>[SHOSUKI153T8] SHORT PLAYA ESTAMPADO KIDS (SAL, 8)</t>
+          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 4)</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -28710,16 +28712,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>SHOSUKI154T1</t>
+          <t>SHOSUKI154T6</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T1] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 1)</t>
+          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 6)</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -28740,16 +28742,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>SHOSUKI154T10</t>
+          <t>SHOSUKI154T8</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T10] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 10)</t>
+          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 8)</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -28770,16 +28772,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>SHOSUKI154T12</t>
+          <t>SHOSUKI155T1</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T12] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 12)</t>
+          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 1)</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -28800,16 +28802,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>SHOSUKI154T14</t>
+          <t>SHOSUKI155T12</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T14] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 14)</t>
+          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 12)</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -28830,16 +28832,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>SHOSUKI154T2</t>
+          <t>SHOSUKI155T14</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T2] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 2)</t>
+          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -28860,16 +28862,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>SHOSUKI154T4</t>
+          <t>SHOSUKI155T2</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T4] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 4)</t>
+          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 2)</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -28890,16 +28892,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SHOSUKI154T6</t>
+          <t>SHOSUKI155T4</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T6] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 6)</t>
+          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 4)</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -28920,16 +28922,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>SHOSUKI154T8</t>
+          <t>SHOSUKI155T6</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>[SHOSUKI154T8] SHORT PLAYA ESTAMPADO KIDS (SOMBRERO, 8)</t>
+          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 6)</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -28950,12 +28952,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>SHOSUKI155T1</t>
+          <t>SHOSUKI155T8</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T1] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 1)</t>
+          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 8)</t>
         </is>
       </c>
       <c r="D480" t="n">
@@ -28980,16 +28982,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>SHOSUKI155T12</t>
+          <t>SHOSUKI156T1</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T12] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 12)</t>
+          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 1)</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -29010,12 +29012,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>SHOSUKI155T14</t>
+          <t>SHOSUKI156T10</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T14] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 14)</t>
+          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 10)</t>
         </is>
       </c>
       <c r="D482" t="n">
@@ -29040,12 +29042,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>SHOSUKI155T2</t>
+          <t>SHOSUKI156T12</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T2] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 2)</t>
+          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 12)</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -29070,16 +29072,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>SHOSUKI155T4</t>
+          <t>SHOSUKI156T14</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T4] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 4)</t>
+          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 14)</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -29100,16 +29102,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>SHOSUKI155T6</t>
+          <t>SHOSUKI156T2</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T6] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 6)</t>
+          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 2)</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -29130,16 +29132,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>SHOSUKI155T8</t>
+          <t>SHOSUKI156T4</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>[SHOSUKI155T8] SHORT PLAYA ESTAMPADO KIDS (PLAYUELA, 8)</t>
+          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 4)</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -29160,16 +29162,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>SHOSUKI156T1</t>
+          <t>SHOSUKI156T6</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T1] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 1)</t>
+          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 6)</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -29190,12 +29192,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>SHOSUKI156T10</t>
+          <t>SHOSUKI156T8</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T10] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 10)</t>
+          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 8)</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -29220,16 +29222,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>SHOSUKI156T12</t>
+          <t>SHUNTCA157TS</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T12] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 12)</t>
+          <t>[SHUNTCA157TS] SHORT SPORT R1 CAB (Gris, S)</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -29238,7 +29240,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29250,12 +29252,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>SHOSUKI156T14</t>
+          <t>SHUNTCA31TL</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T14] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 14)</t>
+          <t>[SHUNTCA31TL] SHORT SPORT R1 CAB (Gris Oscuro, L)</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -29268,7 +29270,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29280,16 +29282,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>SHOSUKI156T2</t>
+          <t>SHUNTCA31TS</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T2] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 2)</t>
+          <t>[SHUNTCA31TS] SHORT SPORT R1 CAB (Gris Oscuro, S)</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -29298,7 +29300,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29310,16 +29312,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>SHOSUKI156T4</t>
+          <t>SHUNTCA43T2XL</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T4] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 4)</t>
+          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB (Negro, 2XL)</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -29328,7 +29330,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29340,16 +29342,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>SHOSUKI156T6</t>
+          <t>SHUNTCA43TM</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T6] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 6)</t>
+          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB (Negro, M)</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -29358,7 +29360,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29370,16 +29372,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>SHOSUKI156T8</t>
+          <t>SHUNTCA43TS</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>[SHOSUKI156T8] SHORT PLAYA ESTAMPADO KIDS (TUCUPIDO, 8)</t>
+          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB (Negro, S)</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -29388,7 +29390,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29400,16 +29402,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>SHUNTCA43T2XL</t>
+          <t>SHUNTDA157TM</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>[SHUNTCA43T2XL] SHORT SPORT R1 CAB (Negro, 2XL)</t>
+          <t>[SHUNTDA157TM] SHORT SPORT R1 DAMA (Gris, M)</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -29418,7 +29420,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29430,16 +29432,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>SHUNTCA43TM</t>
+          <t>SHUNTDA157TS</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TM] SHORT SPORT R1 CAB (Negro, M)</t>
+          <t>[SHUNTDA157TS] SHORT SPORT R1 DAMA (Gris, S)</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -29448,7 +29450,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29460,16 +29462,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>SHUNTCA43TS</t>
+          <t>SHUNTDA157TXL</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>[SHUNTCA43TS] SHORT SPORT R1 CAB (Negro, S)</t>
+          <t>[SHUNTDA157TXL] SHORT SPORT R1 DAMA (Gris, XL)</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -29478,7 +29480,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29508,7 +29510,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29538,7 +29540,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29568,7 +29570,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29598,7 +29600,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>quants_master</t>
+          <t>r1_quants6</t>
         </is>
       </c>
     </row>
@@ -29883,7 +29885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29894,28 +29896,219 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>sku_remap_from</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>inventory_quantity</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>product_id_method</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>LISTA POR AJUSTE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SHOSPBFCA207TS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SHUNTCA157TS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[SHUNTCA157TS] SHORT SPORT R1 CAB (Gris, S)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LISTA POR AJUSTE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SHOSPBFCA207TL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SHUNTCA31TL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[SHUNTCA31TL] SHORT SPORT R1 CAB (Gris Oscuro, L)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LISTA POR AJUSTE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHOSPBFCA207TS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SHUNTCA31TS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[SHUNTCA31TS] SHORT SPORT R1 CAB (Gris Oscuro, S)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LISTA POR AJUSTE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHOSPBFDA207TM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SHUNTDA157TM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[SHUNTDA157TM] SHORT SPORT R1 DAMA (Gris, M)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LISTA POR AJUSTE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SHOSPBFDA207TS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SHUNTDA157TS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[SHUNTDA157TS] SHORT SPORT R1 DAMA (Gris, S)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LISTA POR AJUSTE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHOSPBFDA207TXL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SHUNTDA157TXL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[SHUNTDA157TXL] SHORT SPORT R1 DAMA (Gris, XL)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>inventory_quantity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>product_id_method</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>SKU No Migrados</t>
         </is>
       </c>
@@ -30213,154 +30406,80 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SHOSPBFCA207TL</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[SHOSPBFCA207TL] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tipo de Producto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Talla</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fallback_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SHOSPBFCA207TM</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[SHOSPBFCA207TM] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R1 </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GRIS C</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SHORT SPORT R1 CAB</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SHOSPBFCA207TS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[SHOSPBFCA207TS] SHORT SPORT R1 CAB CAB Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SHOSPBFDA207TM</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[SHOSPBFDA207TM] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SHOSPBFDA207TS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[SHOSPBFDA207TS] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LISTA POR AJUSTE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SHOSPBFDA207TXL</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[SHOSPBFDA207TXL] SHORT SPORT R1 DAMA Dama Gris Oscuro - 9356</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
       </c>
     </row>
   </sheetData>
